--- a/research/traditional_assets/database/data/qatar/qatar_transportation.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_transportation.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08670320634304551</v>
+        <v>0.08665700313670245</v>
       </c>
       <c r="C2">
-        <v>1215.409754328342</v>
+        <v>1205.465338295379</v>
       </c>
       <c r="D2">
-        <v>1166.009754328342</v>
+        <v>1167.328338295379</v>
       </c>
       <c r="E2">
-        <v>-583.8</v>
+        <v>-572.5369999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>11.263</v>
       </c>
       <c r="G2">
         <v>49.4</v>
@@ -1457,28 +1457,28 @@
         <v>127.425</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.5665289</v>
       </c>
       <c r="N2">
-        <v>127.425</v>
+        <v>126.8584711</v>
       </c>
       <c r="O2">
-        <v>12.7425</v>
+        <v>12.68584711</v>
       </c>
       <c r="P2">
-        <v>114.6825</v>
+        <v>114.17262399</v>
       </c>
       <c r="Q2">
-        <v>173.3825</v>
+        <v>172.87262399</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08670320634304551</v>
+        <v>0.08707505367343682</v>
       </c>
       <c r="T2">
-        <v>0.8198499599185859</v>
+        <v>0.8273031413723911</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>224.9223296463782</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08665700313670245</v>
+        <v>0.08661079993035942</v>
       </c>
       <c r="C3">
-        <v>1205.465338295379</v>
+        <v>1195.523907884222</v>
       </c>
       <c r="D3">
-        <v>1167.328338295379</v>
+        <v>1168.649907884222</v>
       </c>
       <c r="E3">
-        <v>-572.5369999999999</v>
+        <v>-561.274</v>
       </c>
       <c r="F3">
-        <v>11.263</v>
+        <v>22.526</v>
       </c>
       <c r="G3">
         <v>49.4</v>
@@ -1539,28 +1539,28 @@
         <v>127.425</v>
       </c>
       <c r="M3">
-        <v>0.5665289</v>
+        <v>1.1330578</v>
       </c>
       <c r="N3">
-        <v>126.8584711</v>
+        <v>126.2919422</v>
       </c>
       <c r="O3">
-        <v>12.68584711</v>
+        <v>12.62919422</v>
       </c>
       <c r="P3">
-        <v>114.17262399</v>
+        <v>113.66274798</v>
       </c>
       <c r="Q3">
-        <v>172.87262399</v>
+        <v>172.36274798</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08707505367343682</v>
+        <v>0.08745448972485655</v>
       </c>
       <c r="T3">
-        <v>0.8273031413723911</v>
+        <v>0.8349084285701518</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>224.9223296463782</v>
+        <v>112.4611648231891</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08661079993035942</v>
+        <v>0.08656459672401637</v>
       </c>
       <c r="C4">
-        <v>1195.523907884222</v>
+        <v>1185.585473246719</v>
       </c>
       <c r="D4">
-        <v>1168.649907884222</v>
+        <v>1169.974473246719</v>
       </c>
       <c r="E4">
-        <v>-561.274</v>
+        <v>-550.011</v>
       </c>
       <c r="F4">
-        <v>22.526</v>
+        <v>33.78899999999999</v>
       </c>
       <c r="G4">
         <v>49.4</v>
@@ -1621,28 +1621,28 @@
         <v>127.425</v>
       </c>
       <c r="M4">
-        <v>1.1330578</v>
+        <v>1.6995867</v>
       </c>
       <c r="N4">
-        <v>126.2919422</v>
+        <v>125.7254133</v>
       </c>
       <c r="O4">
-        <v>12.62919422</v>
+        <v>12.57254133</v>
       </c>
       <c r="P4">
-        <v>113.66274798</v>
+        <v>113.15287197</v>
       </c>
       <c r="Q4">
-        <v>172.36274798</v>
+        <v>171.85287197</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08745448972485655</v>
+        <v>0.08784174920001687</v>
       </c>
       <c r="T4">
-        <v>0.8349084285701518</v>
+        <v>0.8426705258132269</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>112.4611648231891</v>
+        <v>74.97410988212607</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08656459672401637</v>
+        <v>0.08651839351767332</v>
       </c>
       <c r="C5">
-        <v>1185.585473246719</v>
+        <v>1175.650044580791</v>
       </c>
       <c r="D5">
-        <v>1169.974473246719</v>
+        <v>1171.302044580791</v>
       </c>
       <c r="E5">
-        <v>-550.011</v>
+        <v>-538.7479999999999</v>
       </c>
       <c r="F5">
-        <v>33.78899999999999</v>
+        <v>45.052</v>
       </c>
       <c r="G5">
         <v>49.4</v>
@@ -1703,28 +1703,28 @@
         <v>127.425</v>
       </c>
       <c r="M5">
-        <v>1.6995867</v>
+        <v>2.2661156</v>
       </c>
       <c r="N5">
-        <v>125.7254133</v>
+        <v>125.1588844</v>
       </c>
       <c r="O5">
-        <v>12.57254133</v>
+        <v>12.51588844</v>
       </c>
       <c r="P5">
-        <v>113.15287197</v>
+        <v>112.64299596</v>
       </c>
       <c r="Q5">
-        <v>171.85287197</v>
+        <v>171.34299596</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08784174920001687</v>
+        <v>0.08823707658090971</v>
       </c>
       <c r="T5">
-        <v>0.8426705258132269</v>
+        <v>0.8505943334155329</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>74.97410988212607</v>
+        <v>56.23058241159453</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08651839351767332</v>
+        <v>0.08647219031133027</v>
       </c>
       <c r="C6">
-        <v>1175.650044580791</v>
+        <v>1165.7176321307</v>
       </c>
       <c r="D6">
-        <v>1171.302044580791</v>
+        <v>1172.6326321307</v>
       </c>
       <c r="E6">
-        <v>-538.7479999999999</v>
+        <v>-527.4849999999999</v>
       </c>
       <c r="F6">
-        <v>45.052</v>
+        <v>56.315</v>
       </c>
       <c r="G6">
         <v>49.4</v>
@@ -1785,28 +1785,28 @@
         <v>127.425</v>
       </c>
       <c r="M6">
-        <v>2.2661156</v>
+        <v>2.8326445</v>
       </c>
       <c r="N6">
-        <v>125.1588844</v>
+        <v>124.5923555</v>
       </c>
       <c r="O6">
-        <v>12.51588844</v>
+        <v>12.45923555</v>
       </c>
       <c r="P6">
-        <v>112.64299596</v>
+        <v>112.13311995</v>
       </c>
       <c r="Q6">
-        <v>171.34299596</v>
+        <v>170.83311995</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08823707658090971</v>
+        <v>0.08864072664350556</v>
       </c>
       <c r="T6">
-        <v>0.8505943334155329</v>
+        <v>0.8586849580199926</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>56.23058241159453</v>
+        <v>44.98446592927563</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08647219031133027</v>
+        <v>0.08642598710498724</v>
       </c>
       <c r="C7">
-        <v>1165.7176321307</v>
+        <v>1155.788246187311</v>
       </c>
       <c r="D7">
-        <v>1172.6326321307</v>
+        <v>1173.966246187311</v>
       </c>
       <c r="E7">
-        <v>-527.4849999999999</v>
+        <v>-516.222</v>
       </c>
       <c r="F7">
-        <v>56.315</v>
+        <v>67.578</v>
       </c>
       <c r="G7">
         <v>49.4</v>
@@ -1867,28 +1867,28 @@
         <v>127.425</v>
       </c>
       <c r="M7">
-        <v>2.8326445</v>
+        <v>3.3991734</v>
       </c>
       <c r="N7">
-        <v>124.5923555</v>
+        <v>124.0258266</v>
       </c>
       <c r="O7">
-        <v>12.45923555</v>
+        <v>12.40258266</v>
       </c>
       <c r="P7">
-        <v>112.13311995</v>
+        <v>111.62324394</v>
       </c>
       <c r="Q7">
-        <v>170.83311995</v>
+        <v>170.32324394</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08864072664350556</v>
+        <v>0.08905296500530557</v>
       </c>
       <c r="T7">
-        <v>0.8586849580199926</v>
+        <v>0.8669477235734834</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>44.98446592927563</v>
+        <v>37.48705494106302</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08642598710498724</v>
+        <v>0.08637978389864419</v>
       </c>
       <c r="C8">
-        <v>1155.788246187311</v>
+        <v>1145.861897088357</v>
       </c>
       <c r="D8">
-        <v>1173.966246187311</v>
+        <v>1175.302897088357</v>
       </c>
       <c r="E8">
-        <v>-516.222</v>
+        <v>-504.9589999999999</v>
       </c>
       <c r="F8">
-        <v>67.57799999999999</v>
+        <v>78.84099999999999</v>
       </c>
       <c r="G8">
         <v>49.4</v>
@@ -1949,28 +1949,28 @@
         <v>127.425</v>
       </c>
       <c r="M8">
-        <v>3.399173399999999</v>
+        <v>3.965702299999999</v>
       </c>
       <c r="N8">
-        <v>124.0258266</v>
+        <v>123.4592977</v>
       </c>
       <c r="O8">
-        <v>12.40258266</v>
+        <v>12.34592977</v>
       </c>
       <c r="P8">
-        <v>111.62324394</v>
+        <v>111.11336793</v>
       </c>
       <c r="Q8">
-        <v>170.32324394</v>
+        <v>169.81336793</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08905296500530557</v>
+        <v>0.08947406870821956</v>
       </c>
       <c r="T8">
-        <v>0.8669477235734834</v>
+        <v>0.8753881830098449</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.48705494106304</v>
+        <v>32.13176137805402</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08637978389864419</v>
+        <v>0.08633358069230114</v>
       </c>
       <c r="C9">
-        <v>1145.861897088357</v>
+        <v>1135.938595218704</v>
       </c>
       <c r="D9">
-        <v>1175.302897088357</v>
+        <v>1176.642595218704</v>
       </c>
       <c r="E9">
-        <v>-504.9589999999999</v>
+        <v>-493.696</v>
       </c>
       <c r="F9">
-        <v>78.84100000000001</v>
+        <v>90.104</v>
       </c>
       <c r="G9">
         <v>49.4</v>
@@ -2031,28 +2031,28 @@
         <v>127.425</v>
       </c>
       <c r="M9">
-        <v>3.9657023</v>
+        <v>4.5322312</v>
       </c>
       <c r="N9">
-        <v>123.4592977</v>
+        <v>122.8927688</v>
       </c>
       <c r="O9">
-        <v>12.34592977</v>
+        <v>12.28927688</v>
       </c>
       <c r="P9">
-        <v>111.11336793</v>
+        <v>110.60349192</v>
       </c>
       <c r="Q9">
-        <v>169.81336793</v>
+        <v>169.30349192</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08947406870821956</v>
+        <v>0.08990432683945776</v>
       </c>
       <c r="T9">
-        <v>0.875388183009845</v>
+        <v>0.8840121306948231</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.13176137805402</v>
+        <v>28.11529120579727</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08633358069230114</v>
+        <v>0.08628737748595809</v>
       </c>
       <c r="C10">
-        <v>1135.938595218704</v>
+        <v>1126.018351010624</v>
       </c>
       <c r="D10">
-        <v>1176.642595218704</v>
+        <v>1177.985351010624</v>
       </c>
       <c r="E10">
-        <v>-493.696</v>
+        <v>-482.433</v>
       </c>
       <c r="F10">
-        <v>90.104</v>
+        <v>101.367</v>
       </c>
       <c r="G10">
         <v>49.4</v>
@@ -2113,28 +2113,28 @@
         <v>127.425</v>
       </c>
       <c r="M10">
-        <v>4.5322312</v>
+        <v>5.098760099999999</v>
       </c>
       <c r="N10">
-        <v>122.8927688</v>
+        <v>122.3262399</v>
       </c>
       <c r="O10">
-        <v>12.28927688</v>
+        <v>12.23262399</v>
       </c>
       <c r="P10">
-        <v>110.60349192</v>
+        <v>110.09361591</v>
       </c>
       <c r="Q10">
-        <v>169.30349192</v>
+        <v>168.79361591</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08990432683945776</v>
+        <v>0.09034404119336054</v>
       </c>
       <c r="T10">
-        <v>0.8840121306948231</v>
+        <v>0.8928256156915588</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.11529120579727</v>
+        <v>24.99136996070869</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08628737748595809</v>
+        <v>0.08624117427961506</v>
       </c>
       <c r="C11">
-        <v>1126.018351010624</v>
+        <v>1116.101174944061</v>
       </c>
       <c r="D11">
-        <v>1177.985351010624</v>
+        <v>1179.331174944061</v>
       </c>
       <c r="E11">
-        <v>-482.433</v>
+        <v>-471.17</v>
       </c>
       <c r="F11">
-        <v>101.367</v>
+        <v>112.63</v>
       </c>
       <c r="G11">
         <v>49.4</v>
@@ -2195,28 +2195,28 @@
         <v>127.425</v>
       </c>
       <c r="M11">
-        <v>5.098760099999999</v>
+        <v>5.665288999999999</v>
       </c>
       <c r="N11">
-        <v>122.3262399</v>
+        <v>121.759711</v>
       </c>
       <c r="O11">
-        <v>12.23262399</v>
+        <v>12.1759711</v>
       </c>
       <c r="P11">
-        <v>110.09361591</v>
+        <v>109.5837399</v>
       </c>
       <c r="Q11">
-        <v>168.79361591</v>
+        <v>168.2837399</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09034404119336054</v>
+        <v>0.09079352697735006</v>
       </c>
       <c r="T11">
-        <v>0.8928256156915588</v>
+        <v>0.9018349559104446</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.99136996070869</v>
+        <v>22.49223296463782</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08624117427961506</v>
+        <v>0.08619497107327201</v>
       </c>
       <c r="C12">
-        <v>1116.101174944061</v>
+        <v>1106.18707754691</v>
       </c>
       <c r="D12">
-        <v>1179.331174944061</v>
+        <v>1180.68007754691</v>
       </c>
       <c r="E12">
-        <v>-471.17</v>
+        <v>-459.9069999999999</v>
       </c>
       <c r="F12">
-        <v>112.63</v>
+        <v>123.893</v>
       </c>
       <c r="G12">
         <v>49.4</v>
@@ -2277,28 +2277,28 @@
         <v>127.425</v>
       </c>
       <c r="M12">
-        <v>5.665289</v>
+        <v>6.231817899999999</v>
       </c>
       <c r="N12">
-        <v>121.759711</v>
+        <v>121.1931821</v>
       </c>
       <c r="O12">
-        <v>12.1759711</v>
+        <v>12.11931821</v>
       </c>
       <c r="P12">
-        <v>109.5837399</v>
+        <v>109.07386389</v>
       </c>
       <c r="Q12">
-        <v>168.2837399</v>
+        <v>167.77386389</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09079352697735006</v>
+        <v>0.09125311356547416</v>
       </c>
       <c r="T12">
-        <v>0.9018349559104446</v>
+        <v>0.9110467532129004</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.49223296463781</v>
+        <v>20.44748451330711</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08619497107327201</v>
+        <v>0.08614876786692897</v>
       </c>
       <c r="C13">
-        <v>1106.18707754691</v>
+        <v>1096.276069395283</v>
       </c>
       <c r="D13">
-        <v>1180.68007754691</v>
+        <v>1182.032069395283</v>
       </c>
       <c r="E13">
-        <v>-459.9069999999999</v>
+        <v>-448.644</v>
       </c>
       <c r="F13">
-        <v>123.893</v>
+        <v>135.156</v>
       </c>
       <c r="G13">
         <v>49.4</v>
@@ -2359,28 +2359,28 @@
         <v>127.425</v>
       </c>
       <c r="M13">
-        <v>6.231817899999999</v>
+        <v>6.798346799999998</v>
       </c>
       <c r="N13">
-        <v>121.1931821</v>
+        <v>120.6266532</v>
       </c>
       <c r="O13">
-        <v>12.11931821</v>
+        <v>12.06266532</v>
       </c>
       <c r="P13">
-        <v>109.07386389</v>
+        <v>108.56398788</v>
       </c>
       <c r="Q13">
-        <v>167.77386389</v>
+        <v>167.26398788</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09125311356547416</v>
+        <v>0.09172314530332837</v>
       </c>
       <c r="T13">
-        <v>0.9110467532129004</v>
+        <v>0.9204679095449578</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.44748451330711</v>
+        <v>18.74352747053151</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08614876786692897</v>
+        <v>0.08610256466058591</v>
       </c>
       <c r="C14">
-        <v>1096.276069395283</v>
+        <v>1086.368161113796</v>
       </c>
       <c r="D14">
-        <v>1182.032069395283</v>
+        <v>1183.387161113796</v>
       </c>
       <c r="E14">
-        <v>-448.644</v>
+        <v>-437.381</v>
       </c>
       <c r="F14">
-        <v>135.156</v>
+        <v>146.419</v>
       </c>
       <c r="G14">
         <v>49.4</v>
@@ -2441,28 +2441,28 @@
         <v>127.425</v>
       </c>
       <c r="M14">
-        <v>6.798346799999998</v>
+        <v>7.3648757</v>
       </c>
       <c r="N14">
-        <v>120.6266532</v>
+        <v>120.0601243</v>
       </c>
       <c r="O14">
-        <v>12.06266532</v>
+        <v>12.00601243</v>
       </c>
       <c r="P14">
-        <v>108.56398788</v>
+        <v>108.05411187</v>
       </c>
       <c r="Q14">
-        <v>167.26398788</v>
+        <v>166.75411187</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09172314530332837</v>
+        <v>0.09220398236848955</v>
       </c>
       <c r="T14">
-        <v>0.9204679095449578</v>
+        <v>0.9301056441834991</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.74352747053151</v>
+        <v>17.30171766510601</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08610256466058591</v>
+        <v>0.08605636145424288</v>
       </c>
       <c r="C15">
-        <v>1086.368161113796</v>
+        <v>1076.463363375836</v>
       </c>
       <c r="D15">
-        <v>1183.387161113796</v>
+        <v>1184.745363375836</v>
       </c>
       <c r="E15">
-        <v>-437.381</v>
+        <v>-426.1179999999999</v>
       </c>
       <c r="F15">
-        <v>146.419</v>
+        <v>157.682</v>
       </c>
       <c r="G15">
         <v>49.4</v>
@@ -2523,28 +2523,28 @@
         <v>127.425</v>
       </c>
       <c r="M15">
-        <v>7.3648757</v>
+        <v>7.9314046</v>
       </c>
       <c r="N15">
-        <v>120.0601243</v>
+        <v>119.4935954</v>
       </c>
       <c r="O15">
-        <v>12.00601243</v>
+        <v>11.94935954</v>
       </c>
       <c r="P15">
-        <v>108.05411187</v>
+        <v>107.54423586</v>
       </c>
       <c r="Q15">
-        <v>166.75411187</v>
+        <v>166.24423586</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09220398236848955</v>
+        <v>0.09269600169098008</v>
       </c>
       <c r="T15">
-        <v>0.9301056441834991</v>
+        <v>0.9399675121857275</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.30171766510601</v>
+        <v>16.06588068902701</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08605636145424288</v>
+        <v>0.08601015824789983</v>
       </c>
       <c r="C16">
-        <v>1076.463363375836</v>
+        <v>1066.56168690385</v>
       </c>
       <c r="D16">
-        <v>1184.745363375836</v>
+        <v>1186.10668690385</v>
       </c>
       <c r="E16">
-        <v>-426.1179999999999</v>
+        <v>-414.8549999999999</v>
       </c>
       <c r="F16">
-        <v>157.682</v>
+        <v>168.945</v>
       </c>
       <c r="G16">
         <v>49.4</v>
@@ -2605,28 +2605,28 @@
         <v>127.425</v>
       </c>
       <c r="M16">
-        <v>7.9314046</v>
+        <v>8.4979335</v>
       </c>
       <c r="N16">
-        <v>119.4935954</v>
+        <v>118.9270665</v>
       </c>
       <c r="O16">
-        <v>11.94935954</v>
+        <v>11.89270665</v>
       </c>
       <c r="P16">
-        <v>107.54423586</v>
+        <v>107.03435985</v>
       </c>
       <c r="Q16">
-        <v>166.24423586</v>
+        <v>165.73435985</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09269600169098008</v>
+        <v>0.09319959793870568</v>
       </c>
       <c r="T16">
-        <v>0.9399675121857275</v>
+        <v>0.9500614241409496</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.06588068902701</v>
+        <v>14.99482197642521</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08601015824789983</v>
+        <v>0.08596395504155678</v>
       </c>
       <c r="C17">
-        <v>1066.56168690385</v>
+        <v>1056.663142469622</v>
       </c>
       <c r="D17">
-        <v>1186.10668690385</v>
+        <v>1187.471142469622</v>
       </c>
       <c r="E17">
-        <v>-414.855</v>
+        <v>-403.592</v>
       </c>
       <c r="F17">
-        <v>168.945</v>
+        <v>180.208</v>
       </c>
       <c r="G17">
         <v>49.4</v>
@@ -2687,28 +2687,28 @@
         <v>127.425</v>
       </c>
       <c r="M17">
-        <v>8.497933499999998</v>
+        <v>9.0644624</v>
       </c>
       <c r="N17">
-        <v>118.9270665</v>
+        <v>118.3605376</v>
       </c>
       <c r="O17">
-        <v>11.89270665</v>
+        <v>11.83605376</v>
       </c>
       <c r="P17">
-        <v>107.03435985</v>
+        <v>106.52448384</v>
       </c>
       <c r="Q17">
-        <v>165.73435985</v>
+        <v>165.22448384</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09319959793870568</v>
+        <v>0.09371518457328187</v>
       </c>
       <c r="T17">
-        <v>0.9500614241409496</v>
+        <v>0.9603956673332007</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.99482197642521</v>
+        <v>14.05764560289863</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08596395504155678</v>
+        <v>0.08591775183521373</v>
       </c>
       <c r="C18">
-        <v>1056.663142469622</v>
+        <v>1046.767740894561</v>
       </c>
       <c r="D18">
-        <v>1187.471142469622</v>
+        <v>1188.838740894561</v>
       </c>
       <c r="E18">
-        <v>-403.592</v>
+        <v>-392.329</v>
       </c>
       <c r="F18">
-        <v>180.208</v>
+        <v>191.471</v>
       </c>
       <c r="G18">
         <v>49.4</v>
@@ -2769,28 +2769,28 @@
         <v>127.425</v>
       </c>
       <c r="M18">
-        <v>9.0644624</v>
+        <v>9.6309913</v>
       </c>
       <c r="N18">
-        <v>118.3605376</v>
+        <v>117.7940087</v>
       </c>
       <c r="O18">
-        <v>11.83605376</v>
+        <v>11.77940087</v>
       </c>
       <c r="P18">
-        <v>106.52448384</v>
+        <v>106.01460783</v>
       </c>
       <c r="Q18">
-        <v>165.22448384</v>
+        <v>164.71460783</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09371518457328187</v>
+        <v>0.09424319498218522</v>
       </c>
       <c r="T18">
-        <v>0.9603956673332007</v>
+        <v>0.9709789284336987</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.05764560289863</v>
+        <v>13.23072527331636</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08591775183521373</v>
+        <v>0.08611454862887069</v>
       </c>
       <c r="C19">
-        <v>1046.767740894561</v>
+        <v>1029.701385521864</v>
       </c>
       <c r="D19">
-        <v>1188.838740894561</v>
+        <v>1183.035385521864</v>
       </c>
       <c r="E19">
-        <v>-392.329</v>
+        <v>-381.0659999999999</v>
       </c>
       <c r="F19">
-        <v>191.471</v>
+        <v>202.734</v>
       </c>
       <c r="G19">
         <v>49.4</v>
@@ -2851,45 +2851,45 @@
         <v>127.425</v>
       </c>
       <c r="M19">
-        <v>9.6309913</v>
+        <v>10.5016212</v>
       </c>
       <c r="N19">
-        <v>117.7940087</v>
+        <v>116.9233788</v>
       </c>
       <c r="O19">
-        <v>11.77940087</v>
+        <v>11.69233788</v>
       </c>
       <c r="P19">
-        <v>106.01460783</v>
+        <v>105.23104092</v>
       </c>
       <c r="Q19">
-        <v>164.71460783</v>
+        <v>163.93104092</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09424319498218522</v>
+        <v>0.09478408369374475</v>
       </c>
       <c r="T19">
-        <v>0.9709789284336987</v>
+        <v>0.9818203178537211</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.1</v>
       </c>
       <c r="W19">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.23072527331636</v>
+        <v>12.13384082069157</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0861145486288707</v>
+        <v>0.08608184542252764</v>
       </c>
       <c r="C20">
-        <v>1029.701385521864</v>
+        <v>1019.398844257506</v>
       </c>
       <c r="D20">
-        <v>1183.035385521864</v>
+        <v>1183.995844257506</v>
       </c>
       <c r="E20">
-        <v>-381.066</v>
+        <v>-369.803</v>
       </c>
       <c r="F20">
-        <v>202.734</v>
+        <v>213.997</v>
       </c>
       <c r="G20">
         <v>49.4</v>
@@ -2933,28 +2933,28 @@
         <v>127.425</v>
       </c>
       <c r="M20">
-        <v>10.5016212</v>
+        <v>11.0850446</v>
       </c>
       <c r="N20">
-        <v>116.9233788</v>
+        <v>116.3399554</v>
       </c>
       <c r="O20">
-        <v>11.69233788</v>
+        <v>11.63399554</v>
       </c>
       <c r="P20">
-        <v>105.23104092</v>
+        <v>104.70595986</v>
       </c>
       <c r="Q20">
-        <v>163.93104092</v>
+        <v>163.40595986</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09478408369374475</v>
+        <v>0.09533832768213288</v>
       </c>
       <c r="T20">
-        <v>0.9818203178537211</v>
+        <v>0.9929293959013984</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.13384082069157</v>
+        <v>11.49521761960254</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08608184542252764</v>
+        <v>0.08604914221618459</v>
       </c>
       <c r="C21">
-        <v>1019.398844257506</v>
+        <v>1009.097863775738</v>
       </c>
       <c r="D21">
-        <v>1183.995844257506</v>
+        <v>1184.957863775738</v>
       </c>
       <c r="E21">
-        <v>-369.803</v>
+        <v>-358.54</v>
       </c>
       <c r="F21">
-        <v>213.997</v>
+        <v>225.26</v>
       </c>
       <c r="G21">
         <v>49.4</v>
@@ -3015,28 +3015,28 @@
         <v>127.425</v>
       </c>
       <c r="M21">
-        <v>11.0850446</v>
+        <v>11.668468</v>
       </c>
       <c r="N21">
-        <v>116.3399554</v>
+        <v>115.756532</v>
       </c>
       <c r="O21">
-        <v>11.63399554</v>
+        <v>11.5756532</v>
       </c>
       <c r="P21">
-        <v>104.70595986</v>
+        <v>104.1808788</v>
       </c>
       <c r="Q21">
-        <v>163.40595986</v>
+        <v>162.8808788</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09533832768213288</v>
+        <v>0.09590642777023074</v>
       </c>
       <c r="T21">
-        <v>0.9929293959013984</v>
+        <v>1.004316200900268</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.49521761960254</v>
+        <v>10.92045673862241</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08604914221618459</v>
+        <v>0.08601643900984154</v>
       </c>
       <c r="C22">
-        <v>1009.097863775738</v>
+        <v>998.7984478841519</v>
       </c>
       <c r="D22">
-        <v>1184.957863775738</v>
+        <v>1185.921447884152</v>
       </c>
       <c r="E22">
-        <v>-358.54</v>
+        <v>-347.2769999999999</v>
       </c>
       <c r="F22">
-        <v>225.26</v>
+        <v>236.523</v>
       </c>
       <c r="G22">
         <v>49.4</v>
@@ -3097,28 +3097,28 @@
         <v>127.425</v>
       </c>
       <c r="M22">
-        <v>11.668468</v>
+        <v>12.2518914</v>
       </c>
       <c r="N22">
-        <v>115.756532</v>
+        <v>115.1731086</v>
       </c>
       <c r="O22">
-        <v>11.5756532</v>
+        <v>11.51731086</v>
       </c>
       <c r="P22">
-        <v>104.1808788</v>
+        <v>103.65579774</v>
       </c>
       <c r="Q22">
-        <v>162.8808788</v>
+        <v>162.35579774</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09590642777023074</v>
+        <v>0.09648891013903993</v>
       </c>
       <c r="T22">
-        <v>1.004316200900268</v>
+        <v>1.015991279443412</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.92045673862241</v>
+        <v>10.4004349891642</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08601643900984154</v>
+        <v>0.08598373580349851</v>
       </c>
       <c r="C23">
-        <v>998.798447884152</v>
+        <v>988.5006004027339</v>
       </c>
       <c r="D23">
-        <v>1185.921447884152</v>
+        <v>1186.886600402734</v>
       </c>
       <c r="E23">
-        <v>-347.277</v>
+        <v>-336.014</v>
       </c>
       <c r="F23">
-        <v>236.523</v>
+        <v>247.786</v>
       </c>
       <c r="G23">
         <v>49.4</v>
@@ -3179,28 +3179,28 @@
         <v>127.425</v>
       </c>
       <c r="M23">
-        <v>12.2518914</v>
+        <v>12.8353148</v>
       </c>
       <c r="N23">
-        <v>115.1731086</v>
+        <v>114.5896852</v>
       </c>
       <c r="O23">
-        <v>11.51731086</v>
+        <v>11.45896852</v>
       </c>
       <c r="P23">
-        <v>103.65579774</v>
+        <v>103.13071668</v>
       </c>
       <c r="Q23">
-        <v>162.35579774</v>
+        <v>161.83071668</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09648891013903993</v>
+        <v>0.09708632795320321</v>
       </c>
       <c r="T23">
-        <v>1.015991279443412</v>
+        <v>1.027965718974842</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.40043498916421</v>
+        <v>9.927687944202194</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08598373580349851</v>
+        <v>0.08630293259715546</v>
       </c>
       <c r="C24">
-        <v>988.5006004027339</v>
+        <v>967.8839469018621</v>
       </c>
       <c r="D24">
-        <v>1186.886600402734</v>
+        <v>1177.532946901862</v>
       </c>
       <c r="E24">
-        <v>-336.014</v>
+        <v>-324.751</v>
       </c>
       <c r="F24">
-        <v>247.786</v>
+        <v>259.049</v>
       </c>
       <c r="G24">
         <v>49.4</v>
@@ -3261,45 +3261,45 @@
         <v>127.425</v>
       </c>
       <c r="M24">
-        <v>12.8353148</v>
+        <v>13.8591215</v>
       </c>
       <c r="N24">
-        <v>114.5896852</v>
+        <v>113.5658785</v>
       </c>
       <c r="O24">
-        <v>11.45896852</v>
+        <v>11.35658785</v>
       </c>
       <c r="P24">
-        <v>103.13071668</v>
+        <v>102.20929065</v>
       </c>
       <c r="Q24">
-        <v>161.83071668</v>
+        <v>160.90929065</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09708632795320321</v>
+        <v>0.09769926311318891</v>
       </c>
       <c r="T24">
-        <v>1.027965718974842</v>
+        <v>1.040251182909686</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.1</v>
       </c>
       <c r="W24">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>9.927687944202194</v>
+        <v>9.19430571411038</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08630293259715546</v>
+        <v>0.08628552939081241</v>
       </c>
       <c r="C25">
-        <v>967.8839469018621</v>
+        <v>957.1271240263569</v>
       </c>
       <c r="D25">
-        <v>1177.532946901862</v>
+        <v>1178.039124026357</v>
       </c>
       <c r="E25">
-        <v>-324.751</v>
+        <v>-313.4879999999999</v>
       </c>
       <c r="F25">
-        <v>259.049</v>
+        <v>270.312</v>
       </c>
       <c r="G25">
         <v>49.4</v>
@@ -3343,28 +3343,28 @@
         <v>127.425</v>
       </c>
       <c r="M25">
-        <v>13.8591215</v>
+        <v>14.461692</v>
       </c>
       <c r="N25">
-        <v>113.5658785</v>
+        <v>112.963308</v>
       </c>
       <c r="O25">
-        <v>11.35658785</v>
+        <v>11.2963308</v>
       </c>
       <c r="P25">
-        <v>102.20929065</v>
+        <v>101.6669772</v>
       </c>
       <c r="Q25">
-        <v>160.90929065</v>
+        <v>160.3669772</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09769926311318891</v>
+        <v>0.0983283281458058</v>
       </c>
       <c r="T25">
-        <v>1.040251182909686</v>
+        <v>1.052859948527026</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.19430571411038</v>
+        <v>8.811209642689111</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08628552939081241</v>
+        <v>0.08626812618446938</v>
       </c>
       <c r="C26">
-        <v>957.127124026357</v>
+        <v>946.3707365110101</v>
       </c>
       <c r="D26">
-        <v>1178.039124026357</v>
+        <v>1178.54573651101</v>
       </c>
       <c r="E26">
-        <v>-313.488</v>
+        <v>-302.225</v>
       </c>
       <c r="F26">
-        <v>270.312</v>
+        <v>281.575</v>
       </c>
       <c r="G26">
         <v>49.4</v>
@@ -3425,28 +3425,28 @@
         <v>127.425</v>
       </c>
       <c r="M26">
-        <v>14.461692</v>
+        <v>15.0642625</v>
       </c>
       <c r="N26">
-        <v>112.963308</v>
+        <v>112.3607375</v>
       </c>
       <c r="O26">
-        <v>11.2963308</v>
+        <v>11.23607375</v>
       </c>
       <c r="P26">
-        <v>101.6669772</v>
+        <v>101.12466375</v>
       </c>
       <c r="Q26">
-        <v>160.3669772</v>
+        <v>159.82466375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0983283281458058</v>
+        <v>0.09897416824595917</v>
       </c>
       <c r="T26">
-        <v>1.052859948527026</v>
+        <v>1.065804947894162</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.811209642689114</v>
+        <v>8.458761256981548</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08626812618446938</v>
+        <v>0.08625072297812633</v>
       </c>
       <c r="C27">
-        <v>946.3707365110101</v>
+        <v>935.6147849177426</v>
       </c>
       <c r="D27">
-        <v>1178.54573651101</v>
+        <v>1179.052784917742</v>
       </c>
       <c r="E27">
-        <v>-302.225</v>
+        <v>-290.9619999999999</v>
       </c>
       <c r="F27">
-        <v>281.575</v>
+        <v>292.838</v>
       </c>
       <c r="G27">
         <v>49.4</v>
@@ -3507,28 +3507,28 @@
         <v>127.425</v>
       </c>
       <c r="M27">
-        <v>15.0642625</v>
+        <v>15.666833</v>
       </c>
       <c r="N27">
-        <v>112.3607375</v>
+        <v>111.758167</v>
       </c>
       <c r="O27">
-        <v>11.23607375</v>
+        <v>11.1758167</v>
       </c>
       <c r="P27">
-        <v>101.12466375</v>
+        <v>100.5823503</v>
       </c>
       <c r="Q27">
-        <v>159.82466375</v>
+        <v>159.2823503</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09897416824595917</v>
+        <v>0.0996374634839545</v>
       </c>
       <c r="T27">
-        <v>1.065804947894162</v>
+        <v>1.079099812109058</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.458761256981548</v>
+        <v>8.13342428555918</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08625072297812633</v>
+        <v>0.08623331977178328</v>
       </c>
       <c r="C28">
-        <v>935.6147849177426</v>
+        <v>924.8592698094382</v>
       </c>
       <c r="D28">
-        <v>1179.052784917742</v>
+        <v>1179.560269809438</v>
       </c>
       <c r="E28">
-        <v>-290.9619999999999</v>
+        <v>-279.699</v>
       </c>
       <c r="F28">
-        <v>292.838</v>
+        <v>304.101</v>
       </c>
       <c r="G28">
         <v>49.4</v>
@@ -3589,28 +3589,28 @@
         <v>127.425</v>
       </c>
       <c r="M28">
-        <v>15.666833</v>
+        <v>16.2694035</v>
       </c>
       <c r="N28">
-        <v>111.758167</v>
+        <v>111.1555965</v>
       </c>
       <c r="O28">
-        <v>11.1758167</v>
+        <v>11.11555965</v>
       </c>
       <c r="P28">
-        <v>100.5823503</v>
+        <v>100.04003685</v>
       </c>
       <c r="Q28">
-        <v>159.2823503</v>
+        <v>158.74003685</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0996374634839545</v>
+        <v>0.1003189311942237</v>
       </c>
       <c r="T28">
-        <v>1.079099812109058</v>
+        <v>1.092758919179156</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.13342428555918</v>
+        <v>7.83218634905699</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08623331977178328</v>
+        <v>0.08641751656544024</v>
       </c>
       <c r="C29">
-        <v>924.8592698094382</v>
+        <v>908.2470698091381</v>
       </c>
       <c r="D29">
-        <v>1179.560269809438</v>
+        <v>1174.211069809138</v>
       </c>
       <c r="E29">
-        <v>-279.699</v>
+        <v>-268.4359999999999</v>
       </c>
       <c r="F29">
-        <v>304.101</v>
+        <v>315.364</v>
       </c>
       <c r="G29">
         <v>49.4</v>
@@ -3671,45 +3671,45 @@
         <v>127.425</v>
       </c>
       <c r="M29">
-        <v>16.2694035</v>
+        <v>17.1242652</v>
       </c>
       <c r="N29">
-        <v>111.1555965</v>
+        <v>110.3007348</v>
       </c>
       <c r="O29">
-        <v>11.11555965</v>
+        <v>11.03007348</v>
       </c>
       <c r="P29">
-        <v>100.04003685</v>
+        <v>99.27066131999999</v>
       </c>
       <c r="Q29">
-        <v>158.74003685</v>
+        <v>157.97066132</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1003189311942237</v>
+        <v>0.1010193285631114</v>
       </c>
       <c r="T29">
-        <v>1.092758919179156</v>
+        <v>1.106797445890091</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.1</v>
       </c>
       <c r="W29">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.83218634905699</v>
+        <v>7.441195199429635</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08641751656544024</v>
+        <v>0.08640731335909718</v>
       </c>
       <c r="C30">
-        <v>908.2470698091381</v>
+        <v>897.2791082355816</v>
       </c>
       <c r="D30">
-        <v>1174.211069809138</v>
+        <v>1174.506108235581</v>
       </c>
       <c r="E30">
-        <v>-268.4359999999999</v>
+        <v>-257.1729999999999</v>
       </c>
       <c r="F30">
-        <v>315.364</v>
+        <v>326.627</v>
       </c>
       <c r="G30">
         <v>49.4</v>
@@ -3753,28 +3753,28 @@
         <v>127.425</v>
       </c>
       <c r="M30">
-        <v>17.1242652</v>
+        <v>17.7358461</v>
       </c>
       <c r="N30">
-        <v>110.3007348</v>
+        <v>109.6891539</v>
       </c>
       <c r="O30">
-        <v>11.03007348</v>
+        <v>10.96891539</v>
       </c>
       <c r="P30">
-        <v>99.27066131999999</v>
+        <v>98.72023851</v>
       </c>
       <c r="Q30">
-        <v>157.97066132</v>
+        <v>157.42023851</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1010193285631114</v>
+        <v>0.1017394554353482</v>
       </c>
       <c r="T30">
-        <v>1.106797445890091</v>
+        <v>1.121231424057672</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.441195199429635</v>
+        <v>7.18460226151827</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08640731335909718</v>
+        <v>0.08639711015275414</v>
       </c>
       <c r="C31">
-        <v>897.2791082355816</v>
+        <v>886.3112949650903</v>
       </c>
       <c r="D31">
-        <v>1174.506108235581</v>
+        <v>1174.80129496509</v>
       </c>
       <c r="E31">
-        <v>-257.173</v>
+        <v>-245.91</v>
       </c>
       <c r="F31">
-        <v>326.627</v>
+        <v>337.89</v>
       </c>
       <c r="G31">
         <v>49.4</v>
@@ -3835,28 +3835,28 @@
         <v>127.425</v>
       </c>
       <c r="M31">
-        <v>17.7358461</v>
+        <v>18.347427</v>
       </c>
       <c r="N31">
-        <v>109.6891539</v>
+        <v>109.077573</v>
       </c>
       <c r="O31">
-        <v>10.96891539</v>
+        <v>10.9077573</v>
       </c>
       <c r="P31">
-        <v>98.72023851</v>
+        <v>98.1698157</v>
       </c>
       <c r="Q31">
-        <v>157.42023851</v>
+        <v>156.8698157</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1017394554353482</v>
+        <v>0.1024801573610774</v>
       </c>
       <c r="T31">
-        <v>1.121231424057672</v>
+        <v>1.136077801601469</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.184602261518273</v>
+        <v>6.945115519467662</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08639711015275414</v>
+        <v>0.08638690694641109</v>
       </c>
       <c r="C32">
-        <v>886.3112949650903</v>
+        <v>875.343630109511</v>
       </c>
       <c r="D32">
-        <v>1174.80129496509</v>
+        <v>1175.096630109511</v>
       </c>
       <c r="E32">
-        <v>-245.91</v>
+        <v>-234.647</v>
       </c>
       <c r="F32">
-        <v>337.89</v>
+        <v>349.153</v>
       </c>
       <c r="G32">
         <v>49.4</v>
@@ -3917,28 +3917,28 @@
         <v>127.425</v>
       </c>
       <c r="M32">
-        <v>18.347427</v>
+        <v>18.9590079</v>
       </c>
       <c r="N32">
-        <v>109.077573</v>
+        <v>108.4659921</v>
       </c>
       <c r="O32">
-        <v>10.9077573</v>
+        <v>10.84659921</v>
       </c>
       <c r="P32">
-        <v>98.1698157</v>
+        <v>97.61939289</v>
       </c>
       <c r="Q32">
-        <v>156.8698157</v>
+        <v>156.31939289</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1024801573610774</v>
+        <v>0.1032423289078422</v>
       </c>
       <c r="T32">
-        <v>1.136077801601469</v>
+        <v>1.151354508929145</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.945115519467662</v>
+        <v>6.721079534968704</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08638690694641109</v>
+        <v>0.08637670374006803</v>
       </c>
       <c r="C33">
-        <v>875.343630109511</v>
+        <v>864.3761137808026</v>
       </c>
       <c r="D33">
-        <v>1175.096630109511</v>
+        <v>1175.392113780802</v>
       </c>
       <c r="E33">
-        <v>-234.647</v>
+        <v>-223.384</v>
       </c>
       <c r="F33">
-        <v>349.153</v>
+        <v>360.416</v>
       </c>
       <c r="G33">
         <v>49.4</v>
@@ -3999,28 +3999,28 @@
         <v>127.425</v>
       </c>
       <c r="M33">
-        <v>18.9590079</v>
+        <v>19.5705888</v>
       </c>
       <c r="N33">
-        <v>108.4659921</v>
+        <v>107.8544112</v>
       </c>
       <c r="O33">
-        <v>10.84659921</v>
+        <v>10.78544112</v>
       </c>
       <c r="P33">
-        <v>97.61939289</v>
+        <v>97.06897008</v>
       </c>
       <c r="Q33">
-        <v>156.31939289</v>
+        <v>155.76897008</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1032423289078422</v>
+        <v>0.104026917264806</v>
       </c>
       <c r="T33">
-        <v>1.151354508929145</v>
+        <v>1.167080531178222</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.721079534968704</v>
+        <v>6.511045799500933</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08637670374006803</v>
+        <v>0.08636650053372499</v>
       </c>
       <c r="C34">
-        <v>864.3761137808026</v>
+        <v>853.4087460910364</v>
       </c>
       <c r="D34">
-        <v>1175.392113780802</v>
+        <v>1175.687746091036</v>
       </c>
       <c r="E34">
-        <v>-223.384</v>
+        <v>-212.1209999999999</v>
       </c>
       <c r="F34">
-        <v>360.416</v>
+        <v>371.679</v>
       </c>
       <c r="G34">
         <v>49.4</v>
@@ -4081,28 +4081,28 @@
         <v>127.425</v>
       </c>
       <c r="M34">
-        <v>19.5705888</v>
+        <v>20.1821697</v>
       </c>
       <c r="N34">
-        <v>107.8544112</v>
+        <v>107.2428303</v>
       </c>
       <c r="O34">
-        <v>10.78544112</v>
+        <v>10.72428303</v>
       </c>
       <c r="P34">
-        <v>97.06897008</v>
+        <v>96.51854727</v>
       </c>
       <c r="Q34">
-        <v>155.76897008</v>
+        <v>155.21854727</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.104026917264806</v>
+        <v>0.1048349261697388</v>
       </c>
       <c r="T34">
-        <v>1.167080531178222</v>
+        <v>1.183275986927272</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.511045799500933</v>
+        <v>6.313741381334236</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08636650053372499</v>
+        <v>0.08635629732738197</v>
       </c>
       <c r="C35">
-        <v>853.4087460910364</v>
+        <v>842.4415271523967</v>
       </c>
       <c r="D35">
-        <v>1175.687746091036</v>
+        <v>1175.983527152397</v>
       </c>
       <c r="E35">
-        <v>-212.1209999999999</v>
+        <v>-200.8579999999999</v>
       </c>
       <c r="F35">
-        <v>371.679</v>
+        <v>382.942</v>
       </c>
       <c r="G35">
         <v>49.4</v>
@@ -4163,28 +4163,28 @@
         <v>127.425</v>
       </c>
       <c r="M35">
-        <v>20.1821697</v>
+        <v>20.7937506</v>
       </c>
       <c r="N35">
-        <v>107.2428303</v>
+        <v>106.6312494</v>
       </c>
       <c r="O35">
-        <v>10.72428303</v>
+        <v>10.66312494</v>
       </c>
       <c r="P35">
-        <v>96.51854727</v>
+        <v>95.96812446</v>
       </c>
       <c r="Q35">
-        <v>155.21854727</v>
+        <v>154.66812446</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1048349261697388</v>
+        <v>0.105667420193003</v>
       </c>
       <c r="T35">
-        <v>1.183275986927272</v>
+        <v>1.199962214062658</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.313741381334236</v>
+        <v>6.128043105412643</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08635629732738197</v>
+        <v>0.08666109412103892</v>
       </c>
       <c r="C36">
-        <v>842.4415271523967</v>
+        <v>822.406466193684</v>
       </c>
       <c r="D36">
-        <v>1175.983527152397</v>
+        <v>1167.211466193684</v>
       </c>
       <c r="E36">
-        <v>-200.8579999999999</v>
+        <v>-189.5949999999999</v>
       </c>
       <c r="F36">
-        <v>382.942</v>
+        <v>394.205</v>
       </c>
       <c r="G36">
         <v>49.4</v>
@@ -4245,45 +4245,45 @@
         <v>127.425</v>
       </c>
       <c r="M36">
-        <v>20.7937506</v>
+        <v>21.7995365</v>
       </c>
       <c r="N36">
-        <v>106.6312494</v>
+        <v>105.6254635</v>
       </c>
       <c r="O36">
-        <v>10.66312494</v>
+        <v>10.56254635</v>
       </c>
       <c r="P36">
-        <v>95.96812446</v>
+        <v>95.06291714999999</v>
       </c>
       <c r="Q36">
-        <v>154.66812446</v>
+        <v>153.76291715</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.105667420193003</v>
+        <v>0.106525529416983</v>
       </c>
       <c r="T36">
-        <v>1.199962214062658</v>
+        <v>1.217161863571439</v>
       </c>
       <c r="U36">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.1</v>
       </c>
       <c r="W36">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>6.128043105412643</v>
+        <v>5.845307766061906</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08666109412103892</v>
+        <v>0.08665989091469586</v>
       </c>
       <c r="C37">
-        <v>822.406466193684</v>
+        <v>811.1778372164249</v>
       </c>
       <c r="D37">
-        <v>1167.211466193684</v>
+        <v>1167.245837216425</v>
       </c>
       <c r="E37">
-        <v>-189.5949999999999</v>
+        <v>-178.3319999999999</v>
       </c>
       <c r="F37">
-        <v>394.205</v>
+        <v>405.468</v>
       </c>
       <c r="G37">
         <v>49.4</v>
@@ -4327,28 +4327,28 @@
         <v>127.425</v>
       </c>
       <c r="M37">
-        <v>21.7995365</v>
+        <v>22.4223804</v>
       </c>
       <c r="N37">
-        <v>105.6254635</v>
+        <v>105.0026196</v>
       </c>
       <c r="O37">
-        <v>10.56254635</v>
+        <v>10.50026196</v>
       </c>
       <c r="P37">
-        <v>95.06291714999999</v>
+        <v>94.50235764</v>
       </c>
       <c r="Q37">
-        <v>153.76291715</v>
+        <v>153.20235764</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.106525529416983</v>
+        <v>0.1074104545542123</v>
       </c>
       <c r="T37">
-        <v>1.217161863571439</v>
+        <v>1.23489900212737</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.845307766061906</v>
+        <v>5.682938105893521</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08665989091469586</v>
+        <v>0.08665868770835282</v>
       </c>
       <c r="C38">
-        <v>811.177837216425</v>
+        <v>799.9492102634806</v>
       </c>
       <c r="D38">
-        <v>1167.245837216425</v>
+        <v>1167.280210263481</v>
       </c>
       <c r="E38">
-        <v>-178.332</v>
+        <v>-167.069</v>
       </c>
       <c r="F38">
-        <v>405.468</v>
+        <v>416.731</v>
       </c>
       <c r="G38">
         <v>49.4</v>
@@ -4409,28 +4409,28 @@
         <v>127.425</v>
       </c>
       <c r="M38">
-        <v>22.4223804</v>
+        <v>23.0452243</v>
       </c>
       <c r="N38">
-        <v>105.0026196</v>
+        <v>104.3797757</v>
       </c>
       <c r="O38">
-        <v>10.50026196</v>
+        <v>10.43797757</v>
       </c>
       <c r="P38">
-        <v>94.50235764</v>
+        <v>93.94179813</v>
       </c>
       <c r="Q38">
-        <v>153.20235764</v>
+        <v>152.64179813</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1074104545542123</v>
+        <v>0.108323472552941</v>
       </c>
       <c r="T38">
-        <v>1.23489900212737</v>
+        <v>1.253199224446981</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.682938105893521</v>
+        <v>5.529345184112614</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08665868770835282</v>
+        <v>0.08665748450200977</v>
       </c>
       <c r="C39">
-        <v>799.9492102634806</v>
+        <v>788.7205853350304</v>
       </c>
       <c r="D39">
-        <v>1167.280210263481</v>
+        <v>1167.31458533503</v>
       </c>
       <c r="E39">
-        <v>-167.069</v>
+        <v>-155.806</v>
       </c>
       <c r="F39">
-        <v>416.731</v>
+        <v>427.994</v>
       </c>
       <c r="G39">
         <v>49.4</v>
@@ -4491,28 +4491,28 @@
         <v>127.425</v>
       </c>
       <c r="M39">
-        <v>23.0452243</v>
+        <v>23.6680682</v>
       </c>
       <c r="N39">
-        <v>104.3797757</v>
+        <v>103.7569318</v>
       </c>
       <c r="O39">
-        <v>10.43797757</v>
+        <v>10.37569318</v>
       </c>
       <c r="P39">
-        <v>93.94179813</v>
+        <v>93.38123861999999</v>
       </c>
       <c r="Q39">
-        <v>152.64179813</v>
+        <v>152.08123862</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.108323472552941</v>
+        <v>0.1092659427451771</v>
       </c>
       <c r="T39">
-        <v>1.253199224446981</v>
+        <v>1.272089776518838</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.529345184112614</v>
+        <v>5.383836100320177</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08665748450200977</v>
+        <v>0.08665628129566673</v>
       </c>
       <c r="C40">
-        <v>788.7205853350304</v>
+        <v>777.4919624312531</v>
       </c>
       <c r="D40">
-        <v>1167.31458533503</v>
+        <v>1167.348962431253</v>
       </c>
       <c r="E40">
-        <v>-155.806</v>
+        <v>-144.5429999999999</v>
       </c>
       <c r="F40">
-        <v>427.994</v>
+        <v>439.257</v>
       </c>
       <c r="G40">
         <v>49.4</v>
@@ -4573,28 +4573,28 @@
         <v>127.425</v>
       </c>
       <c r="M40">
-        <v>23.6680682</v>
+        <v>24.2909121</v>
       </c>
       <c r="N40">
-        <v>103.7569318</v>
+        <v>103.1340879</v>
       </c>
       <c r="O40">
-        <v>10.37569318</v>
+        <v>10.31340879</v>
       </c>
       <c r="P40">
-        <v>93.38123861999999</v>
+        <v>92.82067911</v>
       </c>
       <c r="Q40">
-        <v>152.08123862</v>
+        <v>151.52067911</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1092659427451771</v>
+        <v>0.1102393135994537</v>
       </c>
       <c r="T40">
-        <v>1.272089776518838</v>
+        <v>1.291599690953707</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.383836100320177</v>
+        <v>5.245789020824788</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08665628129566673</v>
+        <v>0.08665507808932368</v>
       </c>
       <c r="C41">
-        <v>777.4919624312531</v>
+        <v>766.2633415523278</v>
       </c>
       <c r="D41">
-        <v>1167.348962431253</v>
+        <v>1167.383341552328</v>
       </c>
       <c r="E41">
-        <v>-144.5429999999999</v>
+        <v>-133.28</v>
       </c>
       <c r="F41">
-        <v>439.257</v>
+        <v>450.52</v>
       </c>
       <c r="G41">
         <v>49.4</v>
@@ -4655,28 +4655,28 @@
         <v>127.425</v>
       </c>
       <c r="M41">
-        <v>24.2909121</v>
+        <v>24.913756</v>
       </c>
       <c r="N41">
-        <v>103.1340879</v>
+        <v>102.511244</v>
       </c>
       <c r="O41">
-        <v>10.31340879</v>
+        <v>10.2511244</v>
       </c>
       <c r="P41">
-        <v>92.82067911</v>
+        <v>92.2601196</v>
       </c>
       <c r="Q41">
-        <v>151.52067911</v>
+        <v>150.9601196</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1102393135994537</v>
+        <v>0.1112451301488728</v>
       </c>
       <c r="T41">
-        <v>1.291599690953707</v>
+        <v>1.311759935869738</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.245789020824788</v>
+        <v>5.114644295304169</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08665507808932368</v>
+        <v>0.08665387488298064</v>
       </c>
       <c r="C42">
-        <v>766.2633415523278</v>
+        <v>755.034722698433</v>
       </c>
       <c r="D42">
-        <v>1167.383341552328</v>
+        <v>1167.417722698433</v>
       </c>
       <c r="E42">
-        <v>-133.28</v>
+        <v>-122.0169999999999</v>
       </c>
       <c r="F42">
-        <v>450.52</v>
+        <v>461.783</v>
       </c>
       <c r="G42">
         <v>49.4</v>
@@ -4737,28 +4737,28 @@
         <v>127.425</v>
       </c>
       <c r="M42">
-        <v>24.913756</v>
+        <v>25.5365999</v>
       </c>
       <c r="N42">
-        <v>102.511244</v>
+        <v>101.8884001</v>
       </c>
       <c r="O42">
-        <v>10.2511244</v>
+        <v>10.18884001</v>
       </c>
       <c r="P42">
-        <v>92.2601196</v>
+        <v>91.69956009000001</v>
       </c>
       <c r="Q42">
-        <v>150.9601196</v>
+        <v>150.39956009</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1112451301488728</v>
+        <v>0.1122850421745435</v>
       </c>
       <c r="T42">
-        <v>1.311759935869738</v>
+        <v>1.332603578918515</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.114644295304169</v>
+        <v>4.989896873467481</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08665387488298064</v>
+        <v>0.08665267167663759</v>
       </c>
       <c r="C43">
-        <v>755.034722698433</v>
+        <v>743.8061058697481</v>
       </c>
       <c r="D43">
-        <v>1167.417722698433</v>
+        <v>1167.452105869748</v>
       </c>
       <c r="E43">
-        <v>-122.0169999999999</v>
+        <v>-110.7539999999999</v>
       </c>
       <c r="F43">
-        <v>461.783</v>
+        <v>473.046</v>
       </c>
       <c r="G43">
         <v>49.4</v>
@@ -4819,28 +4819,28 @@
         <v>127.425</v>
       </c>
       <c r="M43">
-        <v>25.5365999</v>
+        <v>26.15944380000001</v>
       </c>
       <c r="N43">
-        <v>101.8884001</v>
+        <v>101.2655562</v>
       </c>
       <c r="O43">
-        <v>10.18884001</v>
+        <v>10.12655562</v>
       </c>
       <c r="P43">
-        <v>91.69956009000001</v>
+        <v>91.13900057999999</v>
       </c>
       <c r="Q43">
-        <v>150.39956009</v>
+        <v>149.83900058</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1122850421745435</v>
+        <v>0.1133608132355821</v>
       </c>
       <c r="T43">
-        <v>1.332603578918515</v>
+        <v>1.354165968279319</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.989896873467481</v>
+        <v>4.871089805051588</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08665267167663761</v>
+        <v>0.08665146847029456</v>
       </c>
       <c r="C44">
-        <v>743.8061058697477</v>
+        <v>732.5774910664513</v>
       </c>
       <c r="D44">
-        <v>1167.452105869748</v>
+        <v>1167.486491066451</v>
       </c>
       <c r="E44">
-        <v>-110.754</v>
+        <v>-99.49099999999999</v>
       </c>
       <c r="F44">
-        <v>473.0459999999999</v>
+        <v>484.309</v>
       </c>
       <c r="G44">
         <v>49.4</v>
@@ -4901,28 +4901,28 @@
         <v>127.425</v>
       </c>
       <c r="M44">
-        <v>26.1594438</v>
+        <v>26.7822877</v>
       </c>
       <c r="N44">
-        <v>101.2655562</v>
+        <v>100.6427123</v>
       </c>
       <c r="O44">
-        <v>10.12655562</v>
+        <v>10.06427123</v>
       </c>
       <c r="P44">
-        <v>91.13900057999999</v>
+        <v>90.57844107</v>
       </c>
       <c r="Q44">
-        <v>149.83900058</v>
+        <v>149.27844107</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1133608132355821</v>
+        <v>0.1144743306496395</v>
       </c>
       <c r="T44">
-        <v>1.354165968279319</v>
+        <v>1.376484932705415</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.871089805051589</v>
+        <v>4.757808646794576</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08665146847029456</v>
+        <v>0.0866502652639515</v>
       </c>
       <c r="C45">
-        <v>732.5774910664513</v>
+        <v>721.3488782887231</v>
       </c>
       <c r="D45">
-        <v>1167.486491066451</v>
+        <v>1167.520878288723</v>
       </c>
       <c r="E45">
-        <v>-99.49099999999999</v>
+        <v>-88.22799999999995</v>
       </c>
       <c r="F45">
-        <v>484.309</v>
+        <v>495.572</v>
       </c>
       <c r="G45">
         <v>49.4</v>
@@ -4983,28 +4983,28 @@
         <v>127.425</v>
       </c>
       <c r="M45">
-        <v>26.7822877</v>
+        <v>27.4051316</v>
       </c>
       <c r="N45">
-        <v>100.6427123</v>
+        <v>100.0198684</v>
       </c>
       <c r="O45">
-        <v>10.06427123</v>
+        <v>10.00198684</v>
       </c>
       <c r="P45">
-        <v>90.57844107</v>
+        <v>90.01788155999999</v>
       </c>
       <c r="Q45">
-        <v>149.27844107</v>
+        <v>148.71788156</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1144743306496395</v>
+        <v>0.1156276165427705</v>
       </c>
       <c r="T45">
-        <v>1.376484932705415</v>
+        <v>1.399601003003872</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.757808646794576</v>
+        <v>4.649676632094698</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0866502652639515</v>
+        <v>0.08664906205760846</v>
       </c>
       <c r="C46">
-        <v>721.3488782887231</v>
+        <v>710.1202675367408</v>
       </c>
       <c r="D46">
-        <v>1167.520878288723</v>
+        <v>1167.555267536741</v>
       </c>
       <c r="E46">
-        <v>-88.22799999999995</v>
+        <v>-76.96499999999997</v>
       </c>
       <c r="F46">
-        <v>495.572</v>
+        <v>506.835</v>
       </c>
       <c r="G46">
         <v>49.4</v>
@@ -5065,28 +5065,28 @@
         <v>127.425</v>
       </c>
       <c r="M46">
-        <v>27.4051316</v>
+        <v>28.0279755</v>
       </c>
       <c r="N46">
-        <v>100.0198684</v>
+        <v>99.3970245</v>
       </c>
       <c r="O46">
-        <v>10.00198684</v>
+        <v>9.93970245</v>
       </c>
       <c r="P46">
-        <v>90.01788155999999</v>
+        <v>89.45732205</v>
       </c>
       <c r="Q46">
-        <v>148.71788156</v>
+        <v>148.15732205</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1156276165427705</v>
+        <v>0.1168228401047426</v>
       </c>
       <c r="T46">
-        <v>1.399601003003872</v>
+        <v>1.423557657676817</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.649676632094698</v>
+        <v>4.546350484714816</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08664906205760846</v>
+        <v>0.08768285885126542</v>
       </c>
       <c r="C47">
-        <v>710.1202675367408</v>
+        <v>670.0384398563494</v>
       </c>
       <c r="D47">
-        <v>1167.555267536741</v>
+        <v>1138.736439856349</v>
       </c>
       <c r="E47">
-        <v>-76.96499999999997</v>
+        <v>-65.702</v>
       </c>
       <c r="F47">
-        <v>506.835</v>
+        <v>518.098</v>
       </c>
       <c r="G47">
         <v>49.4</v>
@@ -5147,45 +5147,45 @@
         <v>127.425</v>
       </c>
       <c r="M47">
-        <v>28.0279755</v>
+        <v>29.9460644</v>
       </c>
       <c r="N47">
-        <v>99.3970245</v>
+        <v>97.4789356</v>
       </c>
       <c r="O47">
-        <v>9.93970245</v>
+        <v>9.747893560000001</v>
       </c>
       <c r="P47">
-        <v>89.45732205</v>
+        <v>87.73104204000001</v>
       </c>
       <c r="Q47">
-        <v>148.15732205</v>
+        <v>146.43104204</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1168228401047426</v>
+        <v>0.1180623312060471</v>
       </c>
       <c r="T47">
-        <v>1.423557657676817</v>
+        <v>1.448401595856168</v>
       </c>
       <c r="U47">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V47">
         <v>0.1</v>
       </c>
       <c r="W47">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.546350484714816</v>
+        <v>4.255150135855581</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08768285885126542</v>
+        <v>0.08770415564492237</v>
       </c>
       <c r="C48">
-        <v>670.0384398563494</v>
+        <v>658.1967040575715</v>
       </c>
       <c r="D48">
-        <v>1138.736439856349</v>
+        <v>1138.157704057571</v>
       </c>
       <c r="E48">
-        <v>-65.702</v>
+        <v>-54.43899999999996</v>
       </c>
       <c r="F48">
-        <v>518.098</v>
+        <v>529.361</v>
       </c>
       <c r="G48">
         <v>49.4</v>
@@ -5229,28 +5229,28 @@
         <v>127.425</v>
       </c>
       <c r="M48">
-        <v>29.9460644</v>
+        <v>30.5970658</v>
       </c>
       <c r="N48">
-        <v>97.4789356</v>
+        <v>96.82793419999999</v>
       </c>
       <c r="O48">
-        <v>9.747893560000001</v>
+        <v>9.682793419999999</v>
       </c>
       <c r="P48">
-        <v>87.73104204000001</v>
+        <v>87.14514077999999</v>
       </c>
       <c r="Q48">
-        <v>146.43104204</v>
+        <v>145.84514078</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1180623312060471</v>
+        <v>0.1193485955564573</v>
       </c>
       <c r="T48">
-        <v>1.448401595856168</v>
+        <v>1.474183041136627</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.255150135855581</v>
+        <v>4.164615026582058</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08770415564492237</v>
+        <v>0.08772545243857933</v>
       </c>
       <c r="C49">
-        <v>658.1967040575715</v>
+        <v>646.3555562174759</v>
       </c>
       <c r="D49">
-        <v>1138.157704057571</v>
+        <v>1137.579556217476</v>
       </c>
       <c r="E49">
-        <v>-54.43899999999996</v>
+        <v>-43.17599999999993</v>
       </c>
       <c r="F49">
-        <v>529.361</v>
+        <v>540.624</v>
       </c>
       <c r="G49">
         <v>49.4</v>
@@ -5311,28 +5311,28 @@
         <v>127.425</v>
       </c>
       <c r="M49">
-        <v>30.5970658</v>
+        <v>31.2480672</v>
       </c>
       <c r="N49">
-        <v>96.82793419999999</v>
+        <v>96.17693279999999</v>
       </c>
       <c r="O49">
-        <v>9.682793419999999</v>
+        <v>9.617693279999999</v>
       </c>
       <c r="P49">
-        <v>87.14514077999999</v>
+        <v>86.55923951999999</v>
       </c>
       <c r="Q49">
-        <v>145.84514078</v>
+        <v>145.25923952</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1193485955564573</v>
+        <v>0.1206843316126525</v>
       </c>
       <c r="T49">
-        <v>1.474183041136627</v>
+        <v>1.500956080466334</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.164615026582058</v>
+        <v>4.077852213528265</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08772545243857932</v>
+        <v>0.08929024923223627</v>
       </c>
       <c r="C50">
-        <v>646.3555562174762</v>
+        <v>594.1619827320674</v>
       </c>
       <c r="D50">
-        <v>1137.579556217476</v>
+        <v>1096.648982732067</v>
       </c>
       <c r="E50">
-        <v>-43.17600000000004</v>
+        <v>-31.91300000000001</v>
       </c>
       <c r="F50">
-        <v>540.6239999999999</v>
+        <v>551.8869999999999</v>
       </c>
       <c r="G50">
         <v>49.4</v>
@@ -5393,45 +5393,45 @@
         <v>127.425</v>
       </c>
       <c r="M50">
-        <v>31.2480672</v>
+        <v>33.8306731</v>
       </c>
       <c r="N50">
-        <v>96.1769328</v>
+        <v>93.5943269</v>
       </c>
       <c r="O50">
-        <v>9.617693280000001</v>
+        <v>9.35943269</v>
       </c>
       <c r="P50">
-        <v>86.55923952000001</v>
+        <v>84.23489420999999</v>
       </c>
       <c r="Q50">
-        <v>145.25923952</v>
+        <v>142.93489421</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1206843316126525</v>
+        <v>0.1220724494749731</v>
       </c>
       <c r="T50">
-        <v>1.500956080466334</v>
+        <v>1.52877904290701</v>
       </c>
       <c r="U50">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V50">
         <v>0.1</v>
       </c>
       <c r="W50">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.077852213528266</v>
+        <v>3.766552312552126</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08929024923223627</v>
+        <v>0.08934304602589323</v>
       </c>
       <c r="C51">
-        <v>594.1619827320674</v>
+        <v>581.5692744240863</v>
       </c>
       <c r="D51">
-        <v>1096.648982732067</v>
+        <v>1095.319274424086</v>
       </c>
       <c r="E51">
-        <v>-31.91300000000001</v>
+        <v>-20.64999999999998</v>
       </c>
       <c r="F51">
-        <v>551.8869999999999</v>
+        <v>563.15</v>
       </c>
       <c r="G51">
         <v>49.4</v>
@@ -5475,28 +5475,28 @@
         <v>127.425</v>
       </c>
       <c r="M51">
-        <v>33.8306731</v>
+        <v>34.521095</v>
       </c>
       <c r="N51">
-        <v>93.5943269</v>
+        <v>92.90390500000001</v>
       </c>
       <c r="O51">
-        <v>9.35943269</v>
+        <v>9.290390500000001</v>
       </c>
       <c r="P51">
-        <v>84.23489420999999</v>
+        <v>83.61351450000001</v>
       </c>
       <c r="Q51">
-        <v>142.93489421</v>
+        <v>142.3135145</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1220724494749731</v>
+        <v>0.1235160920517865</v>
       </c>
       <c r="T51">
-        <v>1.52877904290701</v>
+        <v>1.557714923845313</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.766552312552126</v>
+        <v>3.691221266301084</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08934304602589323</v>
+        <v>0.08939584281955018</v>
       </c>
       <c r="C52">
-        <v>581.5692744240863</v>
+        <v>568.9797868055393</v>
       </c>
       <c r="D52">
-        <v>1095.319274424086</v>
+        <v>1093.992786805539</v>
       </c>
       <c r="E52">
-        <v>-20.64999999999998</v>
+        <v>-9.386999999999944</v>
       </c>
       <c r="F52">
-        <v>563.15</v>
+        <v>574.413</v>
       </c>
       <c r="G52">
         <v>49.4</v>
@@ -5557,28 +5557,28 @@
         <v>127.425</v>
       </c>
       <c r="M52">
-        <v>34.521095</v>
+        <v>35.2115169</v>
       </c>
       <c r="N52">
-        <v>92.90390500000001</v>
+        <v>92.21348309999999</v>
       </c>
       <c r="O52">
-        <v>9.290390500000001</v>
+        <v>9.22134831</v>
       </c>
       <c r="P52">
-        <v>83.61351450000001</v>
+        <v>82.99213478999999</v>
       </c>
       <c r="Q52">
-        <v>142.3135145</v>
+        <v>141.69213479</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1235160920517865</v>
+        <v>0.1250186588154085</v>
       </c>
       <c r="T52">
-        <v>1.557714923845313</v>
+        <v>1.587831861148445</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.691221266301084</v>
+        <v>3.618844378726552</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08939584281955018</v>
+        <v>0.08944863961320715</v>
       </c>
       <c r="C53">
-        <v>568.9797868055393</v>
+        <v>556.3935081893209</v>
       </c>
       <c r="D53">
-        <v>1093.992786805539</v>
+        <v>1092.669508189321</v>
       </c>
       <c r="E53">
-        <v>-9.386999999999944</v>
+        <v>1.87600000000009</v>
       </c>
       <c r="F53">
-        <v>574.413</v>
+        <v>585.676</v>
       </c>
       <c r="G53">
         <v>49.4</v>
@@ -5639,28 +5639,28 @@
         <v>127.425</v>
       </c>
       <c r="M53">
-        <v>35.2115169</v>
+        <v>35.9019388</v>
       </c>
       <c r="N53">
-        <v>92.21348309999999</v>
+        <v>91.5230612</v>
       </c>
       <c r="O53">
-        <v>9.22134831</v>
+        <v>9.15230612</v>
       </c>
       <c r="P53">
-        <v>82.99213478999999</v>
+        <v>82.37075508</v>
       </c>
       <c r="Q53">
-        <v>141.69213479</v>
+        <v>141.07075508</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1250186588154085</v>
+        <v>0.1265838325275149</v>
       </c>
       <c r="T53">
-        <v>1.587831861148445</v>
+        <v>1.619203670839207</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.618844378726552</v>
+        <v>3.549251217597195</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08944863961320715</v>
+        <v>0.09083703640686409</v>
       </c>
       <c r="C54">
-        <v>556.3935081893209</v>
+        <v>511.4458130421609</v>
       </c>
       <c r="D54">
-        <v>1092.669508189321</v>
+        <v>1058.984813042161</v>
       </c>
       <c r="E54">
-        <v>1.87600000000009</v>
+        <v>13.13900000000001</v>
       </c>
       <c r="F54">
-        <v>585.676</v>
+        <v>596.939</v>
       </c>
       <c r="G54">
         <v>49.4</v>
@@ -5721,45 +5721,45 @@
         <v>127.425</v>
       </c>
       <c r="M54">
-        <v>35.9019388</v>
+        <v>38.2637899</v>
       </c>
       <c r="N54">
-        <v>91.5230612</v>
+        <v>89.16121010000001</v>
       </c>
       <c r="O54">
-        <v>9.15230612</v>
+        <v>8.916121010000001</v>
       </c>
       <c r="P54">
-        <v>82.37075508</v>
+        <v>80.24508909000001</v>
       </c>
       <c r="Q54">
-        <v>141.07075508</v>
+        <v>138.94508909</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1265838325275149</v>
+        <v>0.1282156093763066</v>
       </c>
       <c r="T54">
-        <v>1.619203670839207</v>
+        <v>1.651910451155108</v>
       </c>
       <c r="U54">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V54">
         <v>0.1</v>
       </c>
       <c r="W54">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.549251217597195</v>
+        <v>3.330171954555918</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09083703640686409</v>
+        <v>0.09091503320052105</v>
       </c>
       <c r="C55">
-        <v>511.4458130421609</v>
+        <v>498.3519949292365</v>
       </c>
       <c r="D55">
-        <v>1058.984813042161</v>
+        <v>1057.153994929236</v>
       </c>
       <c r="E55">
-        <v>13.13900000000001</v>
+        <v>24.40200000000004</v>
       </c>
       <c r="F55">
-        <v>596.939</v>
+        <v>608.202</v>
       </c>
       <c r="G55">
         <v>49.4</v>
@@ -5803,28 +5803,28 @@
         <v>127.425</v>
       </c>
       <c r="M55">
-        <v>38.2637899</v>
+        <v>38.9857482</v>
       </c>
       <c r="N55">
-        <v>89.16121010000001</v>
+        <v>88.43925179999999</v>
       </c>
       <c r="O55">
-        <v>8.916121010000001</v>
+        <v>8.843925179999999</v>
       </c>
       <c r="P55">
-        <v>80.24508909000001</v>
+        <v>79.59532661999999</v>
       </c>
       <c r="Q55">
-        <v>138.94508909</v>
+        <v>138.29532662</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1282156093763066</v>
+        <v>0.129918333044611</v>
       </c>
       <c r="T55">
-        <v>1.651910451155108</v>
+        <v>1.686039265397788</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.330171954555918</v>
+        <v>3.268502103545623</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09091503320052105</v>
+        <v>0.09099302999417802</v>
       </c>
       <c r="C56">
-        <v>498.3519949292365</v>
+        <v>485.2644962838314</v>
       </c>
       <c r="D56">
-        <v>1057.153994929236</v>
+        <v>1055.329496283831</v>
       </c>
       <c r="E56">
-        <v>24.40200000000004</v>
+        <v>35.66500000000008</v>
       </c>
       <c r="F56">
-        <v>608.202</v>
+        <v>619.465</v>
       </c>
       <c r="G56">
         <v>49.4</v>
@@ -5885,28 +5885,28 @@
         <v>127.425</v>
       </c>
       <c r="M56">
-        <v>38.9857482</v>
+        <v>39.70770650000001</v>
       </c>
       <c r="N56">
-        <v>88.43925179999999</v>
+        <v>87.71729349999998</v>
       </c>
       <c r="O56">
-        <v>8.843925179999999</v>
+        <v>8.771729349999999</v>
       </c>
       <c r="P56">
-        <v>79.59532661999999</v>
+        <v>78.94556414999998</v>
       </c>
       <c r="Q56">
-        <v>138.29532662</v>
+        <v>137.64556415</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.129918333044611</v>
+        <v>0.1316967333203956</v>
       </c>
       <c r="T56">
-        <v>1.686039265397788</v>
+        <v>1.721684915829031</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.268502103545623</v>
+        <v>3.209074792572066</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09099302999417802</v>
+        <v>0.09107102678783495</v>
       </c>
       <c r="C57">
-        <v>485.2644962838314</v>
+        <v>472.1832844427904</v>
       </c>
       <c r="D57">
-        <v>1055.329496283831</v>
+        <v>1053.51128444279</v>
       </c>
       <c r="E57">
-        <v>35.66500000000008</v>
+        <v>46.92800000000011</v>
       </c>
       <c r="F57">
-        <v>619.465</v>
+        <v>630.7280000000001</v>
       </c>
       <c r="G57">
         <v>49.4</v>
@@ -5967,28 +5967,28 @@
         <v>127.425</v>
       </c>
       <c r="M57">
-        <v>39.70770650000001</v>
+        <v>40.4296648</v>
       </c>
       <c r="N57">
-        <v>87.71729349999998</v>
+        <v>86.9953352</v>
       </c>
       <c r="O57">
-        <v>8.771729349999999</v>
+        <v>8.699533520000001</v>
       </c>
       <c r="P57">
-        <v>78.94556414999998</v>
+        <v>78.29580168</v>
       </c>
       <c r="Q57">
-        <v>137.64556415</v>
+        <v>136.99580168</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1316967333203956</v>
+        <v>0.1335559699723522</v>
       </c>
       <c r="T57">
-        <v>1.721684915829031</v>
+        <v>1.758950823098057</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.209074792572066</v>
+        <v>3.151769885561851</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09107102678783495</v>
+        <v>0.09114902358149191</v>
       </c>
       <c r="C58">
-        <v>472.1832844427904</v>
+        <v>459.1083269676684</v>
       </c>
       <c r="D58">
-        <v>1053.51128444279</v>
+        <v>1051.699326967668</v>
       </c>
       <c r="E58">
-        <v>46.92800000000011</v>
+        <v>58.19100000000014</v>
       </c>
       <c r="F58">
-        <v>630.7280000000001</v>
+        <v>641.9910000000001</v>
       </c>
       <c r="G58">
         <v>49.4</v>
@@ -6049,28 +6049,28 @@
         <v>127.425</v>
       </c>
       <c r="M58">
-        <v>40.4296648</v>
+        <v>41.15162310000001</v>
       </c>
       <c r="N58">
-        <v>86.9953352</v>
+        <v>86.27337689999999</v>
       </c>
       <c r="O58">
-        <v>8.699533520000001</v>
+        <v>8.627337689999999</v>
       </c>
       <c r="P58">
-        <v>78.29580168</v>
+        <v>77.64603920999998</v>
       </c>
       <c r="Q58">
-        <v>136.99580168</v>
+        <v>136.34603921</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1335559699723522</v>
+        <v>0.1355016827476556</v>
       </c>
       <c r="T58">
-        <v>1.758950823098057</v>
+        <v>1.797950028379597</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.151769885561851</v>
+        <v>3.096475677043221</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09114902358149191</v>
+        <v>0.09122702037514888</v>
       </c>
       <c r="C59">
-        <v>459.1083269676684</v>
+        <v>446.0395916428057</v>
       </c>
       <c r="D59">
-        <v>1051.699326967668</v>
+        <v>1049.893591642806</v>
       </c>
       <c r="E59">
-        <v>58.19100000000014</v>
+        <v>69.45400000000006</v>
       </c>
       <c r="F59">
-        <v>641.9910000000001</v>
+        <v>653.254</v>
       </c>
       <c r="G59">
         <v>49.4</v>
@@ -6131,28 +6131,28 @@
         <v>127.425</v>
       </c>
       <c r="M59">
-        <v>41.15162310000001</v>
+        <v>41.87358140000001</v>
       </c>
       <c r="N59">
-        <v>86.27337689999999</v>
+        <v>85.55141859999999</v>
       </c>
       <c r="O59">
-        <v>8.627337689999999</v>
+        <v>8.555141859999999</v>
       </c>
       <c r="P59">
-        <v>77.64603920999998</v>
+        <v>76.99627673999998</v>
       </c>
       <c r="Q59">
-        <v>136.34603921</v>
+        <v>135.69627674</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1355016827476556</v>
+        <v>0.1375400485122592</v>
       </c>
       <c r="T59">
-        <v>1.797950028379597</v>
+        <v>1.838806338674543</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.096475677043221</v>
+        <v>3.043088165370063</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09122702037514888</v>
+        <v>0.09544681716880582</v>
       </c>
       <c r="C60">
-        <v>446.0395916428058</v>
+        <v>345.5394992299821</v>
       </c>
       <c r="D60">
-        <v>1049.893591642806</v>
+        <v>960.656499229982</v>
       </c>
       <c r="E60">
-        <v>69.45399999999995</v>
+        <v>80.71699999999998</v>
       </c>
       <c r="F60">
-        <v>653.2539999999999</v>
+        <v>664.5169999999999</v>
       </c>
       <c r="G60">
         <v>49.4</v>
@@ -6213,45 +6213,45 @@
         <v>127.425</v>
       </c>
       <c r="M60">
-        <v>41.8735814</v>
+        <v>47.7787723</v>
       </c>
       <c r="N60">
-        <v>85.55141860000001</v>
+        <v>79.6462277</v>
       </c>
       <c r="O60">
-        <v>8.555141860000001</v>
+        <v>7.96462277</v>
       </c>
       <c r="P60">
-        <v>76.99627674</v>
+        <v>71.68160492999999</v>
       </c>
       <c r="Q60">
-        <v>135.69627674</v>
+        <v>130.38160493</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1375400485122592</v>
+        <v>0.1396778467531849</v>
       </c>
       <c r="T60">
-        <v>1.838806338674543</v>
+        <v>1.881655639715583</v>
       </c>
       <c r="U60">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V60">
         <v>0.1</v>
       </c>
       <c r="W60">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.043088165370063</v>
+        <v>2.666979368994795</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09544681716880582</v>
+        <v>0.09559501396246277</v>
       </c>
       <c r="C61">
-        <v>345.5394992299821</v>
+        <v>331.417453681789</v>
       </c>
       <c r="D61">
-        <v>960.656499229982</v>
+        <v>957.797453681789</v>
       </c>
       <c r="E61">
-        <v>80.71699999999998</v>
+        <v>91.98000000000002</v>
       </c>
       <c r="F61">
-        <v>664.5169999999999</v>
+        <v>675.78</v>
       </c>
       <c r="G61">
         <v>49.4</v>
@@ -6295,28 +6295,28 @@
         <v>127.425</v>
       </c>
       <c r="M61">
-        <v>47.7787723</v>
+        <v>48.588582</v>
       </c>
       <c r="N61">
-        <v>79.6462277</v>
+        <v>78.83641799999999</v>
       </c>
       <c r="O61">
-        <v>7.96462277</v>
+        <v>7.883641799999999</v>
       </c>
       <c r="P61">
-        <v>71.68160492999999</v>
+        <v>70.95277619999999</v>
       </c>
       <c r="Q61">
-        <v>130.38160493</v>
+        <v>129.6527762</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1396778467531849</v>
+        <v>0.1419225349061569</v>
       </c>
       <c r="T61">
-        <v>1.881655639715583</v>
+        <v>1.926647405808677</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.666979368994795</v>
+        <v>2.622529712844882</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09559501396246277</v>
+        <v>0.09574321075611975</v>
       </c>
       <c r="C62">
-        <v>331.417453681789</v>
+        <v>317.3123754601546</v>
       </c>
       <c r="D62">
-        <v>957.797453681789</v>
+        <v>954.9553754601546</v>
       </c>
       <c r="E62">
-        <v>91.98000000000002</v>
+        <v>103.2430000000001</v>
       </c>
       <c r="F62">
-        <v>675.78</v>
+        <v>687.043</v>
       </c>
       <c r="G62">
         <v>49.4</v>
@@ -6377,28 +6377,28 @@
         <v>127.425</v>
       </c>
       <c r="M62">
-        <v>48.588582</v>
+        <v>49.3983917</v>
       </c>
       <c r="N62">
-        <v>78.83641799999999</v>
+        <v>78.02660829999999</v>
       </c>
       <c r="O62">
-        <v>7.883641799999999</v>
+        <v>7.80266083</v>
       </c>
       <c r="P62">
-        <v>70.95277619999999</v>
+        <v>70.22394747</v>
       </c>
       <c r="Q62">
-        <v>129.6527762</v>
+        <v>128.92394747</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1419225349061569</v>
+        <v>0.1442823352721019</v>
       </c>
       <c r="T62">
-        <v>1.926647405808677</v>
+        <v>1.973946441957826</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.622529712844882</v>
+        <v>2.579537422470375</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09574321075611975</v>
+        <v>0.09589140754977668</v>
       </c>
       <c r="C63">
-        <v>317.3123754601546</v>
+        <v>303.2241139701872</v>
       </c>
       <c r="D63">
-        <v>954.9553754601546</v>
+        <v>952.1301139701872</v>
       </c>
       <c r="E63">
-        <v>103.2430000000001</v>
+        <v>114.506</v>
       </c>
       <c r="F63">
-        <v>687.043</v>
+        <v>698.3059999999999</v>
       </c>
       <c r="G63">
         <v>49.4</v>
@@ -6459,28 +6459,28 @@
         <v>127.425</v>
       </c>
       <c r="M63">
-        <v>49.3983917</v>
+        <v>50.2082014</v>
       </c>
       <c r="N63">
-        <v>78.02660829999999</v>
+        <v>77.2167986</v>
       </c>
       <c r="O63">
-        <v>7.80266083</v>
+        <v>7.721679860000001</v>
       </c>
       <c r="P63">
-        <v>70.22394747</v>
+        <v>69.49511874000001</v>
       </c>
       <c r="Q63">
-        <v>128.92394747</v>
+        <v>128.19511874</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1442823352721019</v>
+        <v>0.1467663356573071</v>
       </c>
       <c r="T63">
-        <v>1.973946441957826</v>
+        <v>2.023734901062193</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.579537422470375</v>
+        <v>2.537931980172466</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09589140754977668</v>
+        <v>0.09825090434343364</v>
       </c>
       <c r="C64">
-        <v>303.2241139701872</v>
+        <v>249.1296703720533</v>
       </c>
       <c r="D64">
-        <v>952.1301139701872</v>
+        <v>909.2986703720533</v>
       </c>
       <c r="E64">
-        <v>114.506</v>
+        <v>125.769</v>
       </c>
       <c r="F64">
-        <v>698.3059999999999</v>
+        <v>709.569</v>
       </c>
       <c r="G64">
         <v>49.4</v>
@@ -6541,45 +6541,45 @@
         <v>127.425</v>
       </c>
       <c r="M64">
-        <v>50.2082014</v>
+        <v>53.7853302</v>
       </c>
       <c r="N64">
-        <v>77.2167986</v>
+        <v>73.63966979999999</v>
       </c>
       <c r="O64">
-        <v>7.721679860000001</v>
+        <v>7.36396698</v>
       </c>
       <c r="P64">
-        <v>69.49511874000001</v>
+        <v>66.27570281999999</v>
       </c>
       <c r="Q64">
-        <v>128.19511874</v>
+        <v>124.97570282</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1467663356573071</v>
+        <v>0.1493846063336044</v>
       </c>
       <c r="T64">
-        <v>2.023734901062193</v>
+        <v>2.076214628226257</v>
       </c>
       <c r="U64">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V64">
         <v>0.1</v>
       </c>
       <c r="W64">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.537931980172466</v>
+        <v>2.369140424092813</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09825090434343364</v>
+        <v>0.09843420113709059</v>
       </c>
       <c r="C65">
-        <v>249.1296703720533</v>
+        <v>234.7000690528538</v>
       </c>
       <c r="D65">
-        <v>909.2986703720533</v>
+        <v>906.1320690528538</v>
       </c>
       <c r="E65">
-        <v>125.769</v>
+        <v>137.032</v>
       </c>
       <c r="F65">
-        <v>709.569</v>
+        <v>720.832</v>
       </c>
       <c r="G65">
         <v>49.4</v>
@@ -6623,28 +6623,28 @@
         <v>127.425</v>
       </c>
       <c r="M65">
-        <v>53.7853302</v>
+        <v>54.6390656</v>
       </c>
       <c r="N65">
-        <v>73.63966979999999</v>
+        <v>72.7859344</v>
       </c>
       <c r="O65">
-        <v>7.36396698</v>
+        <v>7.278593440000001</v>
       </c>
       <c r="P65">
-        <v>66.27570281999999</v>
+        <v>65.50734096000001</v>
       </c>
       <c r="Q65">
-        <v>124.97570282</v>
+        <v>124.20734096</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1493846063336044</v>
+        <v>0.1521483364919183</v>
       </c>
       <c r="T65">
-        <v>2.076214628226257</v>
+        <v>2.131609895788324</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.369140424092813</v>
+        <v>2.332122604966363</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09843420113709059</v>
+        <v>0.09861749793074756</v>
       </c>
       <c r="C66">
-        <v>234.7000690528538</v>
+        <v>220.2924463540483</v>
       </c>
       <c r="D66">
-        <v>906.1320690528538</v>
+        <v>902.9874463540483</v>
       </c>
       <c r="E66">
-        <v>137.032</v>
+        <v>148.2950000000001</v>
       </c>
       <c r="F66">
-        <v>720.832</v>
+        <v>732.095</v>
       </c>
       <c r="G66">
         <v>49.4</v>
@@ -6705,28 +6705,28 @@
         <v>127.425</v>
       </c>
       <c r="M66">
-        <v>54.6390656</v>
+        <v>55.49280100000001</v>
       </c>
       <c r="N66">
-        <v>72.7859344</v>
+        <v>71.932199</v>
       </c>
       <c r="O66">
-        <v>7.278593440000001</v>
+        <v>7.1932199</v>
       </c>
       <c r="P66">
-        <v>65.50734096000001</v>
+        <v>64.73897909999999</v>
       </c>
       <c r="Q66">
-        <v>124.20734096</v>
+        <v>123.4389791</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1521483364919183</v>
+        <v>0.1550699940878502</v>
       </c>
       <c r="T66">
-        <v>2.131609895788324</v>
+        <v>2.19017060721108</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.332122604966363</v>
+        <v>2.296243795659188</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09861749793074756</v>
+        <v>0.09880079472440451</v>
       </c>
       <c r="C67">
-        <v>220.2924463540483</v>
+        <v>205.9065742444917</v>
       </c>
       <c r="D67">
-        <v>902.9874463540483</v>
+        <v>899.8645742444918</v>
       </c>
       <c r="E67">
-        <v>148.2950000000001</v>
+        <v>159.5580000000001</v>
       </c>
       <c r="F67">
-        <v>732.095</v>
+        <v>743.3580000000001</v>
       </c>
       <c r="G67">
         <v>49.4</v>
@@ -6787,28 +6787,28 @@
         <v>127.425</v>
       </c>
       <c r="M67">
-        <v>55.49280100000001</v>
+        <v>56.34653640000001</v>
       </c>
       <c r="N67">
-        <v>71.932199</v>
+        <v>71.07846359999999</v>
       </c>
       <c r="O67">
-        <v>7.1932199</v>
+        <v>7.10784636</v>
       </c>
       <c r="P67">
-        <v>64.73897909999999</v>
+        <v>63.97061724</v>
       </c>
       <c r="Q67">
-        <v>123.4389791</v>
+        <v>122.67061724</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1550699940878502</v>
+        <v>0.1581635138953074</v>
       </c>
       <c r="T67">
-        <v>2.19017060721108</v>
+        <v>2.252176066364586</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.296243795659188</v>
+        <v>2.261452222997685</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09880079472440451</v>
+        <v>0.09898409151806145</v>
       </c>
       <c r="C68">
-        <v>205.9065742444917</v>
+        <v>191.5422278366383</v>
       </c>
       <c r="D68">
-        <v>899.8645742444918</v>
+        <v>896.7632278366383</v>
       </c>
       <c r="E68">
-        <v>159.5580000000001</v>
+        <v>170.821</v>
       </c>
       <c r="F68">
-        <v>743.3580000000001</v>
+        <v>754.621</v>
       </c>
       <c r="G68">
         <v>49.4</v>
@@ -6869,28 +6869,28 @@
         <v>127.425</v>
       </c>
       <c r="M68">
-        <v>56.34653640000001</v>
+        <v>57.2002718</v>
       </c>
       <c r="N68">
-        <v>71.07846359999999</v>
+        <v>70.22472819999999</v>
       </c>
       <c r="O68">
-        <v>7.10784636</v>
+        <v>7.022472819999999</v>
       </c>
       <c r="P68">
-        <v>63.97061724</v>
+        <v>63.20225537999999</v>
       </c>
       <c r="Q68">
-        <v>122.67061724</v>
+        <v>121.90225538</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1581635138953074</v>
+        <v>0.1614445197517014</v>
       </c>
       <c r="T68">
-        <v>2.252176066364586</v>
+        <v>2.317939432133457</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.261452222997685</v>
+        <v>2.227699204743988</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09898409151806145</v>
+        <v>0.09916738831171842</v>
       </c>
       <c r="C69">
-        <v>191.5422278366383</v>
+        <v>177.1991853325565</v>
       </c>
       <c r="D69">
-        <v>896.7632278366383</v>
+        <v>893.6831853325565</v>
       </c>
       <c r="E69">
-        <v>170.821</v>
+        <v>182.0840000000001</v>
       </c>
       <c r="F69">
-        <v>754.621</v>
+        <v>765.884</v>
       </c>
       <c r="G69">
         <v>49.4</v>
@@ -6951,28 +6951,28 @@
         <v>127.425</v>
       </c>
       <c r="M69">
-        <v>57.2002718</v>
+        <v>58.05400720000001</v>
       </c>
       <c r="N69">
-        <v>70.22472819999999</v>
+        <v>69.37099279999998</v>
       </c>
       <c r="O69">
-        <v>7.022472819999999</v>
+        <v>6.937099279999998</v>
       </c>
       <c r="P69">
-        <v>63.20225537999999</v>
+        <v>62.43389351999998</v>
       </c>
       <c r="Q69">
-        <v>121.90225538</v>
+        <v>121.13389352</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1614445197517014</v>
+        <v>0.1649305884741201</v>
       </c>
       <c r="T69">
-        <v>2.317939432133457</v>
+        <v>2.387813008262882</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.227699204743988</v>
+        <v>2.194938922321283</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09916738831171842</v>
+        <v>0.09935068510537537</v>
       </c>
       <c r="C70">
-        <v>177.1991853325565</v>
+        <v>162.8772279710541</v>
       </c>
       <c r="D70">
-        <v>893.6831853325565</v>
+        <v>890.6242279710542</v>
       </c>
       <c r="E70">
-        <v>182.0840000000001</v>
+        <v>193.3470000000001</v>
       </c>
       <c r="F70">
-        <v>765.884</v>
+        <v>777.147</v>
       </c>
       <c r="G70">
         <v>49.4</v>
@@ -7033,28 +7033,28 @@
         <v>127.425</v>
       </c>
       <c r="M70">
-        <v>58.05400720000001</v>
+        <v>58.90774260000001</v>
       </c>
       <c r="N70">
-        <v>69.37099279999998</v>
+        <v>68.51725739999999</v>
       </c>
       <c r="O70">
-        <v>6.937099279999998</v>
+        <v>6.851725739999999</v>
       </c>
       <c r="P70">
-        <v>62.43389351999998</v>
+        <v>61.66553165999999</v>
       </c>
       <c r="Q70">
-        <v>121.13389352</v>
+        <v>120.36553166</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1649305884741201</v>
+        <v>0.1686415648560496</v>
       </c>
       <c r="T70">
-        <v>2.387813008262882</v>
+        <v>2.462194557045818</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.194938922321283</v>
+        <v>2.163128213302134</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09935068510537537</v>
+        <v>0.09953398189903231</v>
       </c>
       <c r="C71">
-        <v>162.8772279710541</v>
+        <v>148.5761399758812</v>
       </c>
       <c r="D71">
-        <v>890.6242279710542</v>
+        <v>887.5861399758813</v>
       </c>
       <c r="E71">
-        <v>193.3470000000001</v>
+        <v>204.6100000000001</v>
       </c>
       <c r="F71">
-        <v>777.147</v>
+        <v>788.4100000000001</v>
       </c>
       <c r="G71">
         <v>49.4</v>
@@ -7115,28 +7115,28 @@
         <v>127.425</v>
       </c>
       <c r="M71">
-        <v>58.90774260000001</v>
+        <v>59.76147800000001</v>
       </c>
       <c r="N71">
-        <v>68.51725739999999</v>
+        <v>67.66352199999999</v>
       </c>
       <c r="O71">
-        <v>6.851725739999999</v>
+        <v>6.766352199999999</v>
       </c>
       <c r="P71">
-        <v>61.66553165999999</v>
+        <v>60.89716979999999</v>
       </c>
       <c r="Q71">
-        <v>120.36553166</v>
+        <v>119.5971698</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1686415648560496</v>
+        <v>0.1725999396634411</v>
       </c>
       <c r="T71">
-        <v>2.462194557045818</v>
+        <v>2.541534875747617</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.163128213302134</v>
+        <v>2.132226381683532</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09953398189903231</v>
+        <v>0.09971727869268929</v>
       </c>
       <c r="C72">
-        <v>148.5761399758812</v>
+        <v>134.2957085049934</v>
       </c>
       <c r="D72">
-        <v>887.5861399758813</v>
+        <v>884.5687085049934</v>
       </c>
       <c r="E72">
-        <v>204.6100000000001</v>
+        <v>215.873</v>
       </c>
       <c r="F72">
-        <v>788.4100000000001</v>
+        <v>799.673</v>
       </c>
       <c r="G72">
         <v>49.4</v>
@@ -7197,28 +7197,28 @@
         <v>127.425</v>
       </c>
       <c r="M72">
-        <v>59.76147800000001</v>
+        <v>60.6152134</v>
       </c>
       <c r="N72">
-        <v>67.66352199999999</v>
+        <v>66.8097866</v>
       </c>
       <c r="O72">
-        <v>6.766352199999999</v>
+        <v>6.68097866</v>
       </c>
       <c r="P72">
-        <v>60.89716979999999</v>
+        <v>60.12880793999999</v>
       </c>
       <c r="Q72">
-        <v>119.5971698</v>
+        <v>118.82880794</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1725999396634411</v>
+        <v>0.1768313058368596</v>
       </c>
       <c r="T72">
-        <v>2.541534875747617</v>
+        <v>2.626346940566781</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.132226381683532</v>
+        <v>2.102195024195031</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09971727869268929</v>
+        <v>0.09990057548634623</v>
       </c>
       <c r="C73">
-        <v>134.2957085049935</v>
+        <v>120.0357236008468</v>
       </c>
       <c r="D73">
-        <v>884.5687085049934</v>
+        <v>881.5717236008468</v>
       </c>
       <c r="E73">
-        <v>215.8729999999999</v>
+        <v>227.136</v>
       </c>
       <c r="F73">
-        <v>799.6729999999999</v>
+        <v>810.9359999999999</v>
       </c>
       <c r="G73">
         <v>49.4</v>
@@ -7279,28 +7279,28 @@
         <v>127.425</v>
       </c>
       <c r="M73">
-        <v>60.61521339999999</v>
+        <v>61.4689488</v>
       </c>
       <c r="N73">
-        <v>66.8097866</v>
+        <v>65.95605119999999</v>
       </c>
       <c r="O73">
-        <v>6.68097866</v>
+        <v>6.595605119999999</v>
       </c>
       <c r="P73">
-        <v>60.12880793999999</v>
+        <v>59.36044607999999</v>
       </c>
       <c r="Q73">
-        <v>118.82880794</v>
+        <v>118.06044608</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1768313058368596</v>
+        <v>0.1813649124512365</v>
       </c>
       <c r="T73">
-        <v>2.62634694056678</v>
+        <v>2.717217010015884</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.102195024195032</v>
+        <v>2.072997871081212</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09990057548634623</v>
+        <v>0.1000838722800032</v>
       </c>
       <c r="C74">
-        <v>120.0357236008468</v>
+        <v>105.7959781416953</v>
       </c>
       <c r="D74">
-        <v>881.5717236008468</v>
+        <v>878.5949781416953</v>
       </c>
       <c r="E74">
-        <v>227.136</v>
+        <v>238.399</v>
       </c>
       <c r="F74">
-        <v>810.9359999999999</v>
+        <v>822.199</v>
       </c>
       <c r="G74">
         <v>49.4</v>
@@ -7361,28 +7361,28 @@
         <v>127.425</v>
       </c>
       <c r="M74">
-        <v>61.4689488</v>
+        <v>62.3226842</v>
       </c>
       <c r="N74">
-        <v>65.95605119999999</v>
+        <v>65.10231579999999</v>
       </c>
       <c r="O74">
-        <v>6.595605119999999</v>
+        <v>6.510231579999999</v>
       </c>
       <c r="P74">
-        <v>59.36044607999999</v>
+        <v>58.59208421999999</v>
       </c>
       <c r="Q74">
-        <v>118.06044608</v>
+        <v>117.29208422</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1813649124512365</v>
+        <v>0.1862343417777896</v>
       </c>
       <c r="T74">
-        <v>2.717217010015884</v>
+        <v>2.814818195720478</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.072997871081212</v>
+        <v>2.04460063997051</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1000838722800032</v>
+        <v>0.1002671690736601</v>
       </c>
       <c r="C75">
-        <v>105.7959781416953</v>
+        <v>91.57626779387658</v>
       </c>
       <c r="D75">
-        <v>878.5949781416953</v>
+        <v>875.6382677938766</v>
       </c>
       <c r="E75">
-        <v>238.399</v>
+        <v>249.662</v>
       </c>
       <c r="F75">
-        <v>822.199</v>
+        <v>833.462</v>
       </c>
       <c r="G75">
         <v>49.4</v>
@@ -7443,28 +7443,28 @@
         <v>127.425</v>
       </c>
       <c r="M75">
-        <v>62.3226842</v>
+        <v>63.1764196</v>
       </c>
       <c r="N75">
-        <v>65.10231579999999</v>
+        <v>64.24858039999999</v>
       </c>
       <c r="O75">
-        <v>6.510231579999999</v>
+        <v>6.42485804</v>
       </c>
       <c r="P75">
-        <v>58.59208421999999</v>
+        <v>57.82372235999999</v>
       </c>
       <c r="Q75">
-        <v>117.29208422</v>
+        <v>116.52372236</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1862343417777896</v>
+        <v>0.1914783425910005</v>
       </c>
       <c r="T75">
-        <v>2.814818195720478</v>
+        <v>2.919927164940809</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.04460063997051</v>
+        <v>2.01697090159253</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1002671690736601</v>
+        <v>0.1100354658673171</v>
       </c>
       <c r="C76">
-        <v>91.57626779387658</v>
+        <v>-52.84517307992508</v>
       </c>
       <c r="D76">
-        <v>875.6382677938766</v>
+        <v>742.4798269200749</v>
       </c>
       <c r="E76">
-        <v>249.662</v>
+        <v>260.925</v>
       </c>
       <c r="F76">
-        <v>833.462</v>
+        <v>844.7249999999999</v>
       </c>
       <c r="G76">
         <v>49.4</v>
@@ -7525,45 +7525,45 @@
         <v>127.425</v>
       </c>
       <c r="M76">
-        <v>63.1764196</v>
+        <v>76.02524999999999</v>
       </c>
       <c r="N76">
-        <v>64.24858039999999</v>
+        <v>51.39975000000001</v>
       </c>
       <c r="O76">
-        <v>6.42485804</v>
+        <v>5.139975000000002</v>
       </c>
       <c r="P76">
-        <v>57.82372235999999</v>
+        <v>46.25977500000001</v>
       </c>
       <c r="Q76">
-        <v>116.52372236</v>
+        <v>104.959775</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1914783425910005</v>
+        <v>0.1971418634692684</v>
       </c>
       <c r="T76">
-        <v>2.919927164940809</v>
+        <v>3.033444851698768</v>
       </c>
       <c r="U76">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V76">
         <v>0.1</v>
       </c>
       <c r="W76">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y76">
-        <v>2.01697090159253</v>
+        <v>1.676087878698196</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1100354658673171</v>
+        <v>0.1103465626609741</v>
       </c>
       <c r="C77">
-        <v>-52.84517307992508</v>
+        <v>-67.68672295132637</v>
       </c>
       <c r="D77">
-        <v>742.4798269200749</v>
+        <v>738.9012770486736</v>
       </c>
       <c r="E77">
-        <v>260.925</v>
+        <v>272.188</v>
       </c>
       <c r="F77">
-        <v>844.7249999999999</v>
+        <v>855.9879999999999</v>
       </c>
       <c r="G77">
         <v>49.4</v>
@@ -7607,28 +7607,28 @@
         <v>127.425</v>
       </c>
       <c r="M77">
-        <v>76.02524999999999</v>
+        <v>77.03891999999999</v>
       </c>
       <c r="N77">
-        <v>51.39975000000001</v>
+        <v>50.38608000000001</v>
       </c>
       <c r="O77">
-        <v>5.139975000000002</v>
+        <v>5.038608000000001</v>
       </c>
       <c r="P77">
-        <v>46.25977500000001</v>
+        <v>45.347472</v>
       </c>
       <c r="Q77">
-        <v>104.959775</v>
+        <v>104.047472</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1971418634692684</v>
+        <v>0.2032773444207252</v>
       </c>
       <c r="T77">
-        <v>3.033444851698768</v>
+        <v>3.156422345686556</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.676087878698196</v>
+        <v>1.654034090820588</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1103465626609741</v>
+        <v>0.110657659454631</v>
       </c>
       <c r="C78">
-        <v>-67.68672295132637</v>
+        <v>-82.493943018035</v>
       </c>
       <c r="D78">
-        <v>738.9012770486736</v>
+        <v>735.357056981965</v>
       </c>
       <c r="E78">
-        <v>272.188</v>
+        <v>283.451</v>
       </c>
       <c r="F78">
-        <v>855.9879999999999</v>
+        <v>867.251</v>
       </c>
       <c r="G78">
         <v>49.4</v>
@@ -7689,28 +7689,28 @@
         <v>127.425</v>
       </c>
       <c r="M78">
-        <v>77.03891999999999</v>
+        <v>78.05259</v>
       </c>
       <c r="N78">
-        <v>50.38608000000001</v>
+        <v>49.37241</v>
       </c>
       <c r="O78">
-        <v>5.038608000000001</v>
+        <v>4.937241</v>
       </c>
       <c r="P78">
-        <v>45.347472</v>
+        <v>44.435169</v>
       </c>
       <c r="Q78">
-        <v>104.047472</v>
+        <v>103.135169</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2032773444207252</v>
+        <v>0.2099463454549174</v>
       </c>
       <c r="T78">
-        <v>3.156422345686556</v>
+        <v>3.290093534803717</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.654034090820588</v>
+        <v>1.632553128602139</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.110657659454631</v>
+        <v>0.1109687562482879</v>
       </c>
       <c r="C79">
-        <v>-82.493943018035</v>
+        <v>-97.26732492172687</v>
       </c>
       <c r="D79">
-        <v>735.357056981965</v>
+        <v>731.8466750782732</v>
       </c>
       <c r="E79">
-        <v>283.451</v>
+        <v>294.7140000000001</v>
       </c>
       <c r="F79">
-        <v>867.251</v>
+        <v>878.514</v>
       </c>
       <c r="G79">
         <v>49.4</v>
@@ -7771,28 +7771,28 @@
         <v>127.425</v>
       </c>
       <c r="M79">
-        <v>78.05259</v>
+        <v>79.06626</v>
       </c>
       <c r="N79">
-        <v>49.37241</v>
+        <v>48.35874</v>
       </c>
       <c r="O79">
-        <v>4.937241</v>
+        <v>4.835874</v>
       </c>
       <c r="P79">
-        <v>44.435169</v>
+        <v>43.52286599999999</v>
       </c>
       <c r="Q79">
-        <v>103.135169</v>
+        <v>102.222866</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2099463454549174</v>
+        <v>0.2172216193103998</v>
       </c>
       <c r="T79">
-        <v>3.290093534803717</v>
+        <v>3.435916650204256</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.632553128602139</v>
+        <v>1.611622960286727</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1109687562482879</v>
+        <v>0.1112798530419449</v>
       </c>
       <c r="C80">
-        <v>-97.26732492172687</v>
+        <v>-112.0073509608586</v>
       </c>
       <c r="D80">
-        <v>731.8466750782732</v>
+        <v>728.3696490391414</v>
       </c>
       <c r="E80">
-        <v>294.7140000000001</v>
+        <v>305.9770000000001</v>
       </c>
       <c r="F80">
-        <v>878.514</v>
+        <v>889.777</v>
       </c>
       <c r="G80">
         <v>49.4</v>
@@ -7853,28 +7853,28 @@
         <v>127.425</v>
       </c>
       <c r="M80">
-        <v>79.06626</v>
+        <v>80.07993</v>
       </c>
       <c r="N80">
-        <v>48.35874</v>
+        <v>47.34506999999999</v>
       </c>
       <c r="O80">
-        <v>4.835874</v>
+        <v>4.734507</v>
       </c>
       <c r="P80">
-        <v>43.52286599999999</v>
+        <v>42.61056299999999</v>
       </c>
       <c r="Q80">
-        <v>102.222866</v>
+        <v>101.310563</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2172216193103998</v>
+        <v>0.2251897763902139</v>
       </c>
       <c r="T80">
-        <v>3.435916650204256</v>
+        <v>3.595627681357227</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.611622960286727</v>
+        <v>1.591222669650186</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1112798530419449</v>
+        <v>0.1115909498356019</v>
       </c>
       <c r="C81">
-        <v>-112.0073509608586</v>
+        <v>-126.7144943115678</v>
       </c>
       <c r="D81">
-        <v>728.3696490391414</v>
+        <v>724.9255056884322</v>
       </c>
       <c r="E81">
-        <v>305.9770000000001</v>
+        <v>317.24</v>
       </c>
       <c r="F81">
-        <v>889.777</v>
+        <v>901.04</v>
       </c>
       <c r="G81">
         <v>49.4</v>
@@ -7935,28 +7935,28 @@
         <v>127.425</v>
       </c>
       <c r="M81">
-        <v>80.07993</v>
+        <v>81.0936</v>
       </c>
       <c r="N81">
-        <v>47.34506999999999</v>
+        <v>46.3314</v>
       </c>
       <c r="O81">
-        <v>4.734507</v>
+        <v>4.63314</v>
       </c>
       <c r="P81">
-        <v>42.61056299999999</v>
+        <v>41.69826</v>
       </c>
       <c r="Q81">
-        <v>101.310563</v>
+        <v>100.39826</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2251897763902139</v>
+        <v>0.2339547491780094</v>
       </c>
       <c r="T81">
-        <v>3.595627681357227</v>
+        <v>3.771309815625496</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.591222669650186</v>
+        <v>1.571332386279559</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1115909498356019</v>
+        <v>0.1119020466292588</v>
       </c>
       <c r="C82">
-        <v>-126.7144943115678</v>
+        <v>-141.3892192423355</v>
       </c>
       <c r="D82">
-        <v>724.9255056884322</v>
+        <v>721.5137807576646</v>
       </c>
       <c r="E82">
-        <v>317.24</v>
+        <v>328.503</v>
       </c>
       <c r="F82">
-        <v>901.04</v>
+        <v>912.303</v>
       </c>
       <c r="G82">
         <v>49.4</v>
@@ -8017,28 +8017,28 @@
         <v>127.425</v>
       </c>
       <c r="M82">
-        <v>81.0936</v>
+        <v>82.10727</v>
       </c>
       <c r="N82">
-        <v>46.3314</v>
+        <v>45.31773</v>
       </c>
       <c r="O82">
-        <v>4.63314</v>
+        <v>4.531773</v>
       </c>
       <c r="P82">
-        <v>41.69826</v>
+        <v>40.785957</v>
       </c>
       <c r="Q82">
-        <v>100.39826</v>
+        <v>99.485957</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2339547491780094</v>
+        <v>0.2436423506803096</v>
       </c>
       <c r="T82">
-        <v>3.771309815625496</v>
+        <v>3.96548480613253</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.571332386279559</v>
+        <v>1.551933221016848</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1119020466292588</v>
+        <v>0.1122131434229158</v>
       </c>
       <c r="C83">
-        <v>-141.3892192423355</v>
+        <v>-156.0319813226163</v>
       </c>
       <c r="D83">
-        <v>721.5137807576646</v>
+        <v>718.1340186773838</v>
       </c>
       <c r="E83">
-        <v>328.503</v>
+        <v>339.7660000000001</v>
       </c>
       <c r="F83">
-        <v>912.303</v>
+        <v>923.566</v>
       </c>
       <c r="G83">
         <v>49.4</v>
@@ -8099,28 +8099,28 @@
         <v>127.425</v>
       </c>
       <c r="M83">
-        <v>82.10727</v>
+        <v>83.12094</v>
       </c>
       <c r="N83">
-        <v>45.31773</v>
+        <v>44.30405999999999</v>
       </c>
       <c r="O83">
-        <v>4.531773</v>
+        <v>4.430406</v>
       </c>
       <c r="P83">
-        <v>40.785957</v>
+        <v>39.87365399999999</v>
       </c>
       <c r="Q83">
-        <v>99.485957</v>
+        <v>98.573654</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2436423506803096</v>
+        <v>0.2544063523495321</v>
       </c>
       <c r="T83">
-        <v>3.96548480613253</v>
+        <v>4.181234795584789</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.551933221016848</v>
+        <v>1.533007206126398</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1122131434229158</v>
+        <v>0.1125242402165727</v>
       </c>
       <c r="C84">
-        <v>-156.0319813226163</v>
+        <v>-170.6432276256297</v>
       </c>
       <c r="D84">
-        <v>718.1340186773838</v>
+        <v>714.7857723743704</v>
       </c>
       <c r="E84">
-        <v>339.7660000000001</v>
+        <v>351.0290000000001</v>
       </c>
       <c r="F84">
-        <v>923.566</v>
+        <v>934.8290000000001</v>
       </c>
       <c r="G84">
         <v>49.4</v>
@@ -8181,28 +8181,28 @@
         <v>127.425</v>
       </c>
       <c r="M84">
-        <v>83.12094</v>
+        <v>84.13461000000001</v>
       </c>
       <c r="N84">
-        <v>44.30405999999999</v>
+        <v>43.29038999999999</v>
       </c>
       <c r="O84">
-        <v>4.430406</v>
+        <v>4.329038999999999</v>
       </c>
       <c r="P84">
-        <v>39.87365399999999</v>
+        <v>38.96135099999999</v>
       </c>
       <c r="Q84">
-        <v>98.573654</v>
+        <v>97.661351</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2544063523495321</v>
+        <v>0.2664367071563102</v>
       </c>
       <c r="T84">
-        <v>4.181234795584789</v>
+        <v>4.422367136737315</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.533007206126398</v>
+        <v>1.514537239787526</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1125242402165727</v>
+        <v>0.1570772818513939</v>
       </c>
       <c r="C85">
-        <v>-170.6432276256297</v>
+        <v>-468.0911500710031</v>
       </c>
       <c r="D85">
-        <v>714.7857723743704</v>
+        <v>428.600849928997</v>
       </c>
       <c r="E85">
-        <v>351.0290000000001</v>
+        <v>362.2920000000001</v>
       </c>
       <c r="F85">
-        <v>934.8290000000001</v>
+        <v>946.0920000000001</v>
       </c>
       <c r="G85">
         <v>49.4</v>
@@ -8263,45 +8263,45 @@
         <v>127.425</v>
       </c>
       <c r="M85">
-        <v>84.13461000000001</v>
+        <v>138.8863056</v>
       </c>
       <c r="N85">
-        <v>43.29038999999999</v>
+        <v>-11.46130560000002</v>
       </c>
       <c r="O85">
-        <v>4.329038999999999</v>
+        <v>-1.146130560000002</v>
       </c>
       <c r="P85">
-        <v>38.96135099999999</v>
+        <v>-10.31517504000002</v>
       </c>
       <c r="Q85">
-        <v>97.661351</v>
+        <v>48.38482495999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2664367071563102</v>
+        <v>0.2817429689537918</v>
       </c>
       <c r="T85">
-        <v>4.422367136737315</v>
+        <v>4.72916064372854</v>
       </c>
       <c r="U85">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1</v>
+        <v>0.09174770647798122</v>
       </c>
       <c r="W85">
-        <v>0.081</v>
+        <v>0.1333314366890324</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y85">
-        <v>1.514537239787526</v>
+        <v>0.9174770647798122</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1570772818513939</v>
+        <v>0.1580872818513939</v>
       </c>
       <c r="C86">
-        <v>-468.0911500710029</v>
+        <v>-483.2093227253842</v>
       </c>
       <c r="D86">
-        <v>428.600849928997</v>
+        <v>424.7456772746157</v>
       </c>
       <c r="E86">
-        <v>362.2919999999999</v>
+        <v>373.5549999999999</v>
       </c>
       <c r="F86">
-        <v>946.0919999999999</v>
+        <v>957.3549999999999</v>
       </c>
       <c r="G86">
         <v>49.4</v>
@@ -8345,37 +8345,37 @@
         <v>127.425</v>
       </c>
       <c r="M86">
-        <v>138.8863056</v>
+        <v>140.539714</v>
       </c>
       <c r="N86">
-        <v>-11.46130559999999</v>
+        <v>-13.11471400000001</v>
       </c>
       <c r="O86">
-        <v>-1.146130559999999</v>
+        <v>-1.311471400000001</v>
       </c>
       <c r="P86">
-        <v>-10.31517503999999</v>
+        <v>-11.80324260000001</v>
       </c>
       <c r="Q86">
-        <v>48.38482496000002</v>
+        <v>46.8967574</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2817429689537917</v>
+        <v>0.2974725002173778</v>
       </c>
       <c r="T86">
-        <v>4.729160643728537</v>
+        <v>5.044438019977107</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.09174770647798124</v>
+        <v>0.09066832169588733</v>
       </c>
       <c r="W86">
-        <v>0.1333314366890324</v>
+        <v>0.1334898903750437</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.9174770647798123</v>
+        <v>0.9066832169588732</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1580872818513939</v>
+        <v>0.1590972818513939</v>
       </c>
       <c r="C87">
-        <v>-483.2093227253842</v>
+        <v>-498.258760731991</v>
       </c>
       <c r="D87">
-        <v>424.7456772746157</v>
+        <v>420.959239268009</v>
       </c>
       <c r="E87">
-        <v>373.5549999999999</v>
+        <v>384.818</v>
       </c>
       <c r="F87">
-        <v>957.3549999999999</v>
+        <v>968.6179999999999</v>
       </c>
       <c r="G87">
         <v>49.4</v>
@@ -8427,37 +8427,37 @@
         <v>127.425</v>
       </c>
       <c r="M87">
-        <v>140.539714</v>
+        <v>142.1931224</v>
       </c>
       <c r="N87">
-        <v>-13.11471400000001</v>
+        <v>-14.7681224</v>
       </c>
       <c r="O87">
-        <v>-1.311471400000001</v>
+        <v>-1.47681224</v>
       </c>
       <c r="P87">
-        <v>-11.80324260000001</v>
+        <v>-13.29131016</v>
       </c>
       <c r="Q87">
-        <v>46.8967574</v>
+        <v>45.40868984000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2974725002173778</v>
+        <v>0.3154491073757619</v>
       </c>
       <c r="T87">
-        <v>5.044438019977107</v>
+        <v>5.404755021404043</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.09066832169588733</v>
+        <v>0.08961403888547004</v>
       </c>
       <c r="W87">
-        <v>0.1334898903750437</v>
+        <v>0.133644659091613</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.9066832169588732</v>
+        <v>0.8961403888547004</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1590972818513939</v>
+        <v>0.1601072818513939</v>
       </c>
       <c r="C88">
-        <v>-498.258760731991</v>
+        <v>-513.2412860743349</v>
       </c>
       <c r="D88">
-        <v>420.959239268009</v>
+        <v>417.2397139256651</v>
       </c>
       <c r="E88">
-        <v>384.818</v>
+        <v>396.081</v>
       </c>
       <c r="F88">
-        <v>968.6179999999999</v>
+        <v>979.881</v>
       </c>
       <c r="G88">
         <v>49.4</v>
@@ -8509,37 +8509,37 @@
         <v>127.425</v>
       </c>
       <c r="M88">
-        <v>142.1931224</v>
+        <v>143.8465308</v>
       </c>
       <c r="N88">
-        <v>-14.7681224</v>
+        <v>-16.42153080000001</v>
       </c>
       <c r="O88">
-        <v>-1.47681224</v>
+        <v>-1.642153080000001</v>
       </c>
       <c r="P88">
-        <v>-13.29131016</v>
+        <v>-14.77937772000001</v>
       </c>
       <c r="Q88">
-        <v>45.40868984000001</v>
+        <v>43.92062227999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3154491073757619</v>
+        <v>0.3361913464046667</v>
       </c>
       <c r="T88">
-        <v>5.404755021404043</v>
+        <v>5.820505407665892</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.08961403888547004</v>
+        <v>0.08858399246149912</v>
       </c>
       <c r="W88">
-        <v>0.133644659091613</v>
+        <v>0.133795869906652</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8961403888547004</v>
+        <v>0.8858399246149911</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1601072818513939</v>
+        <v>0.1611172818513939</v>
       </c>
       <c r="C89">
-        <v>-513.2412860743349</v>
+        <v>-528.1586569049618</v>
       </c>
       <c r="D89">
-        <v>417.2397139256651</v>
+        <v>413.5853430950382</v>
       </c>
       <c r="E89">
-        <v>396.081</v>
+        <v>407.3440000000001</v>
       </c>
       <c r="F89">
-        <v>979.881</v>
+        <v>991.144</v>
       </c>
       <c r="G89">
         <v>49.4</v>
@@ -8591,37 +8591,37 @@
         <v>127.425</v>
       </c>
       <c r="M89">
-        <v>143.8465308</v>
+        <v>145.4999392</v>
       </c>
       <c r="N89">
-        <v>-16.42153080000001</v>
+        <v>-18.07493920000003</v>
       </c>
       <c r="O89">
-        <v>-1.642153080000001</v>
+        <v>-1.807493920000003</v>
       </c>
       <c r="P89">
-        <v>-14.77937772000001</v>
+        <v>-16.26744528000003</v>
       </c>
       <c r="Q89">
-        <v>43.92062227999999</v>
+        <v>42.43255471999997</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3361913464046667</v>
+        <v>0.3603906252717223</v>
       </c>
       <c r="T89">
-        <v>5.820505407665892</v>
+        <v>6.305547524971383</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.08858399246149912</v>
+        <v>0.08757735618352752</v>
       </c>
       <c r="W89">
-        <v>0.133795869906652</v>
+        <v>0.1339436441122582</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8858399246149911</v>
+        <v>0.8757735618352751</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1611172818513939</v>
+        <v>0.1621272818513939</v>
       </c>
       <c r="C90">
-        <v>-528.1586569049618</v>
+        <v>-543.012570316483</v>
       </c>
       <c r="D90">
-        <v>413.5853430950382</v>
+        <v>409.994429683517</v>
       </c>
       <c r="E90">
-        <v>407.3440000000001</v>
+        <v>418.607</v>
       </c>
       <c r="F90">
-        <v>991.144</v>
+        <v>1002.407</v>
       </c>
       <c r="G90">
         <v>49.4</v>
@@ -8673,37 +8673,37 @@
         <v>127.425</v>
       </c>
       <c r="M90">
-        <v>145.4999392</v>
+        <v>147.1533476</v>
       </c>
       <c r="N90">
-        <v>-18.07493920000003</v>
+        <v>-19.72834759999999</v>
       </c>
       <c r="O90">
-        <v>-1.807493920000003</v>
+        <v>-1.972834759999999</v>
       </c>
       <c r="P90">
-        <v>-16.26744528000003</v>
+        <v>-17.75551283999999</v>
       </c>
       <c r="Q90">
-        <v>42.43255471999997</v>
+        <v>40.94448716000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3603906252717223</v>
+        <v>0.388989773023697</v>
       </c>
       <c r="T90">
-        <v>6.305547524971383</v>
+        <v>6.8787791181506</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.08757735618352752</v>
+        <v>0.08659334094551038</v>
       </c>
       <c r="W90">
-        <v>0.1339436441122582</v>
+        <v>0.1340880975491991</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8757735618352751</v>
+        <v>0.8659334094551038</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1621272818513939</v>
+        <v>0.1631372818513939</v>
       </c>
       <c r="C91">
-        <v>-543.012570316483</v>
+        <v>-557.8046649694918</v>
       </c>
       <c r="D91">
-        <v>409.994429683517</v>
+        <v>406.4653350305081</v>
       </c>
       <c r="E91">
-        <v>418.607</v>
+        <v>429.87</v>
       </c>
       <c r="F91">
-        <v>1002.407</v>
+        <v>1013.67</v>
       </c>
       <c r="G91">
         <v>49.4</v>
@@ -8755,37 +8755,37 @@
         <v>127.425</v>
       </c>
       <c r="M91">
-        <v>147.1533476</v>
+        <v>148.806756</v>
       </c>
       <c r="N91">
-        <v>-19.72834759999999</v>
+        <v>-21.38175600000001</v>
       </c>
       <c r="O91">
-        <v>-1.972834759999999</v>
+        <v>-2.138175600000001</v>
       </c>
       <c r="P91">
-        <v>-17.75551283999999</v>
+        <v>-19.24358040000001</v>
       </c>
       <c r="Q91">
-        <v>40.94448716000001</v>
+        <v>39.45641959999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.388989773023697</v>
+        <v>0.4233087503260669</v>
       </c>
       <c r="T91">
-        <v>6.8787791181506</v>
+        <v>7.566657029965662</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.08659334094551038</v>
+        <v>0.08563119271278247</v>
       </c>
       <c r="W91">
-        <v>0.1340880975491991</v>
+        <v>0.1342293409097635</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8659334094551038</v>
+        <v>0.8563119271278247</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1631372818513939</v>
+        <v>0.1641472818513939</v>
       </c>
       <c r="C92">
-        <v>-557.8046649694918</v>
+        <v>-572.5365235859181</v>
       </c>
       <c r="D92">
-        <v>406.4653350305081</v>
+        <v>402.9964764140819</v>
       </c>
       <c r="E92">
-        <v>429.87</v>
+        <v>441.133</v>
       </c>
       <c r="F92">
-        <v>1013.67</v>
+        <v>1024.933</v>
       </c>
       <c r="G92">
         <v>49.4</v>
@@ -8837,37 +8837,37 @@
         <v>127.425</v>
       </c>
       <c r="M92">
-        <v>148.806756</v>
+        <v>150.4601644</v>
       </c>
       <c r="N92">
-        <v>-21.38175600000001</v>
+        <v>-23.03516440000003</v>
       </c>
       <c r="O92">
-        <v>-2.138175600000001</v>
+        <v>-2.303516440000003</v>
       </c>
       <c r="P92">
-        <v>-19.24358040000001</v>
+        <v>-20.73164796000002</v>
       </c>
       <c r="Q92">
-        <v>39.45641959999999</v>
+        <v>37.96835203999998</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4233087503260669</v>
+        <v>0.4652541670289632</v>
       </c>
       <c r="T92">
-        <v>7.566657029965662</v>
+        <v>8.407396699961847</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.08563119271278247</v>
+        <v>0.08469019059505958</v>
       </c>
       <c r="W92">
-        <v>0.1342293409097635</v>
+        <v>0.1343674800206453</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8563119271278247</v>
+        <v>0.8469019059505958</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1641472818513939</v>
+        <v>0.1651572818513939</v>
       </c>
       <c r="C93">
-        <v>-572.5365235859181</v>
+        <v>-587.2096753157889</v>
       </c>
       <c r="D93">
-        <v>402.9964764140819</v>
+        <v>399.5863246842111</v>
       </c>
       <c r="E93">
-        <v>441.133</v>
+        <v>452.396</v>
       </c>
       <c r="F93">
-        <v>1024.933</v>
+        <v>1036.196</v>
       </c>
       <c r="G93">
         <v>49.4</v>
@@ -8919,37 +8919,37 @@
         <v>127.425</v>
       </c>
       <c r="M93">
-        <v>150.4601644</v>
+        <v>152.1135728</v>
       </c>
       <c r="N93">
-        <v>-23.03516440000003</v>
+        <v>-24.68857280000002</v>
       </c>
       <c r="O93">
-        <v>-2.303516440000003</v>
+        <v>-2.468857280000002</v>
       </c>
       <c r="P93">
-        <v>-20.73164796000002</v>
+        <v>-22.21971552000002</v>
       </c>
       <c r="Q93">
-        <v>37.96835203999998</v>
+        <v>36.48028447999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4652541670289632</v>
+        <v>0.5176859379075837</v>
       </c>
       <c r="T93">
-        <v>8.407396699961847</v>
+        <v>9.45832128745708</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.08469019059505958</v>
+        <v>0.08376964504511329</v>
       </c>
       <c r="W93">
-        <v>0.1343674800206453</v>
+        <v>0.1345026161073774</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8469019059505958</v>
+        <v>0.8376964504511328</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1651572818513939</v>
+        <v>0.1661672818513939</v>
       </c>
       <c r="C94">
-        <v>-587.2096753157889</v>
+        <v>-601.8255979848356</v>
       </c>
       <c r="D94">
-        <v>399.5863246842111</v>
+        <v>396.2334020151645</v>
       </c>
       <c r="E94">
-        <v>452.396</v>
+        <v>463.6590000000001</v>
       </c>
       <c r="F94">
-        <v>1036.196</v>
+        <v>1047.459</v>
       </c>
       <c r="G94">
         <v>49.4</v>
@@ -9001,37 +9001,37 @@
         <v>127.425</v>
       </c>
       <c r="M94">
-        <v>152.1135728</v>
+        <v>153.7669812</v>
       </c>
       <c r="N94">
-        <v>-24.68857280000002</v>
+        <v>-26.34198120000003</v>
       </c>
       <c r="O94">
-        <v>-2.468857280000002</v>
+        <v>-2.634198120000004</v>
       </c>
       <c r="P94">
-        <v>-22.21971552000002</v>
+        <v>-23.70778308000003</v>
       </c>
       <c r="Q94">
-        <v>36.48028447999999</v>
+        <v>34.99221691999998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5176859379075837</v>
+        <v>0.5850982147515242</v>
       </c>
       <c r="T94">
-        <v>9.45832128745708</v>
+        <v>10.80951004280809</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.08376964504511329</v>
+        <v>0.08286889617366044</v>
       </c>
       <c r="W94">
-        <v>0.1345026161073774</v>
+        <v>0.1346348460417067</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8376964504511328</v>
+        <v>0.8286889617366044</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1661672818513939</v>
+        <v>0.1671772818513939</v>
       </c>
       <c r="C95">
-        <v>-601.8255979848356</v>
+        <v>-616.3857202298803</v>
       </c>
       <c r="D95">
-        <v>396.2334020151645</v>
+        <v>392.9362797701197</v>
       </c>
       <c r="E95">
-        <v>463.6590000000001</v>
+        <v>474.922</v>
       </c>
       <c r="F95">
-        <v>1047.459</v>
+        <v>1058.722</v>
       </c>
       <c r="G95">
         <v>49.4</v>
@@ -9083,37 +9083,37 @@
         <v>127.425</v>
       </c>
       <c r="M95">
-        <v>153.7669812</v>
+        <v>155.4203896</v>
       </c>
       <c r="N95">
-        <v>-26.34198120000003</v>
+        <v>-27.99538960000002</v>
       </c>
       <c r="O95">
-        <v>-2.634198120000004</v>
+        <v>-2.799538960000003</v>
       </c>
       <c r="P95">
-        <v>-23.70778308000003</v>
+        <v>-25.19585064000002</v>
       </c>
       <c r="Q95">
-        <v>34.99221691999998</v>
+        <v>33.50414935999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5850982147515242</v>
+        <v>0.6749812505434452</v>
       </c>
       <c r="T95">
-        <v>10.80951004280809</v>
+        <v>12.61109504994278</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.08286889617366044</v>
+        <v>0.081987312171813</v>
       </c>
       <c r="W95">
-        <v>0.1346348460417067</v>
+        <v>0.1347642625731779</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8286889617366044</v>
+        <v>0.81987312171813</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1671772818513939</v>
+        <v>0.1681872818513939</v>
       </c>
       <c r="C96">
-        <v>-616.3857202298803</v>
+        <v>-630.8914235284938</v>
       </c>
       <c r="D96">
-        <v>392.9362797701197</v>
+        <v>389.6935764715064</v>
       </c>
       <c r="E96">
-        <v>474.922</v>
+        <v>486.1850000000002</v>
       </c>
       <c r="F96">
-        <v>1058.722</v>
+        <v>1069.985</v>
       </c>
       <c r="G96">
         <v>49.4</v>
@@ -9165,37 +9165,37 @@
         <v>127.425</v>
       </c>
       <c r="M96">
-        <v>155.4203896</v>
+        <v>157.073798</v>
       </c>
       <c r="N96">
-        <v>-27.99538960000002</v>
+        <v>-29.64879800000004</v>
       </c>
       <c r="O96">
-        <v>-2.799538960000003</v>
+        <v>-2.964879800000004</v>
       </c>
       <c r="P96">
-        <v>-25.19585064000002</v>
+        <v>-26.68391820000004</v>
       </c>
       <c r="Q96">
-        <v>33.50414935999999</v>
+        <v>32.01608179999997</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6749812505434452</v>
+        <v>0.8008175006521345</v>
       </c>
       <c r="T96">
-        <v>12.61109504994278</v>
+        <v>15.13331405993134</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.081987312171813</v>
+        <v>0.08112428783316233</v>
       </c>
       <c r="W96">
-        <v>0.1347642625731779</v>
+        <v>0.1348909545460918</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.81987312171813</v>
+        <v>0.8112428783316232</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1681872818513939</v>
+        <v>0.1691972818513938</v>
       </c>
       <c r="C97">
-        <v>-630.8914235284938</v>
+        <v>-645.3440441289719</v>
       </c>
       <c r="D97">
-        <v>389.6935764715064</v>
+        <v>386.5039558710282</v>
       </c>
       <c r="E97">
-        <v>486.1850000000002</v>
+        <v>497.4480000000001</v>
       </c>
       <c r="F97">
-        <v>1069.985</v>
+        <v>1081.248</v>
       </c>
       <c r="G97">
         <v>49.4</v>
@@ -9247,37 +9247,37 @@
         <v>127.425</v>
       </c>
       <c r="M97">
-        <v>157.073798</v>
+        <v>158.7272064</v>
       </c>
       <c r="N97">
-        <v>-29.64879800000004</v>
+        <v>-31.30220640000003</v>
       </c>
       <c r="O97">
-        <v>-2.964879800000004</v>
+        <v>-3.130220640000003</v>
       </c>
       <c r="P97">
-        <v>-26.68391820000004</v>
+        <v>-28.17198576000003</v>
       </c>
       <c r="Q97">
-        <v>32.01608179999997</v>
+        <v>30.52801423999998</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8008175006521345</v>
+        <v>0.9895718758151685</v>
       </c>
       <c r="T97">
-        <v>15.13331405993134</v>
+        <v>18.91664257491419</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.08112428783316233</v>
+        <v>0.08027924316823357</v>
       </c>
       <c r="W97">
-        <v>0.1348909545460918</v>
+        <v>0.1350150071029033</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8112428783316232</v>
+        <v>0.8027924316823356</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1691972818513939</v>
+        <v>0.2234350203512131</v>
       </c>
       <c r="C98">
-        <v>-645.3440441289716</v>
+        <v>-774.6192494150188</v>
       </c>
       <c r="D98">
-        <v>386.5039558710282</v>
+        <v>268.4917505849812</v>
       </c>
       <c r="E98">
-        <v>497.4479999999999</v>
+        <v>508.711</v>
       </c>
       <c r="F98">
-        <v>1081.248</v>
+        <v>1092.511</v>
       </c>
       <c r="G98">
         <v>49.4</v>
@@ -9329,45 +9329,45 @@
         <v>127.425</v>
       </c>
       <c r="M98">
-        <v>158.7272064</v>
+        <v>219.3762088</v>
       </c>
       <c r="N98">
-        <v>-31.3022064</v>
+        <v>-91.9512088</v>
       </c>
       <c r="O98">
-        <v>-3.130220640000001</v>
+        <v>-9.195120880000001</v>
       </c>
       <c r="P98">
-        <v>-28.17198576</v>
+        <v>-82.75608792</v>
       </c>
       <c r="Q98">
-        <v>30.52801424</v>
+        <v>-24.05608792</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9895718758151658</v>
+        <v>1.332420451080862</v>
       </c>
       <c r="T98">
-        <v>18.91664257491413</v>
+        <v>25.78858284121836</v>
       </c>
       <c r="U98">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.08027924316823358</v>
+        <v>0.05808515002470952</v>
       </c>
       <c r="W98">
-        <v>0.1350150071029033</v>
+        <v>0.1891365018750383</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.8027924316823357</v>
+        <v>0.5808515002470951</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2234350203512131</v>
+        <v>0.2249850203512131</v>
       </c>
       <c r="C99">
-        <v>-774.6192494150188</v>
+        <v>-788.204777339457</v>
       </c>
       <c r="D99">
-        <v>268.4917505849812</v>
+        <v>266.169222660543</v>
       </c>
       <c r="E99">
-        <v>508.711</v>
+        <v>519.9739999999999</v>
       </c>
       <c r="F99">
-        <v>1092.511</v>
+        <v>1103.774</v>
       </c>
       <c r="G99">
         <v>49.4</v>
@@ -9411,37 +9411,37 @@
         <v>127.425</v>
       </c>
       <c r="M99">
-        <v>219.3762088</v>
+        <v>221.6378192</v>
       </c>
       <c r="N99">
-        <v>-91.9512088</v>
+        <v>-94.2128192</v>
       </c>
       <c r="O99">
-        <v>-9.195120880000001</v>
+        <v>-9.42128192</v>
       </c>
       <c r="P99">
-        <v>-82.75608792</v>
+        <v>-84.79153728</v>
       </c>
       <c r="Q99">
-        <v>-24.05608792</v>
+        <v>-26.09153728</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.332420451080862</v>
+        <v>1.975730676621293</v>
       </c>
       <c r="T99">
-        <v>25.78858284121836</v>
+        <v>38.68287426182754</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.05808515002470952</v>
+        <v>0.05749244441221249</v>
       </c>
       <c r="W99">
-        <v>0.1891365018750383</v>
+        <v>0.1892555171620277</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5808515002470951</v>
+        <v>0.5749244441221248</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2249850203512131</v>
+        <v>0.226535020351213</v>
       </c>
       <c r="C100">
-        <v>-788.204777339457</v>
+        <v>-801.7504688417577</v>
       </c>
       <c r="D100">
-        <v>266.169222660543</v>
+        <v>263.8865311582424</v>
       </c>
       <c r="E100">
-        <v>519.9739999999999</v>
+        <v>531.2370000000001</v>
       </c>
       <c r="F100">
-        <v>1103.774</v>
+        <v>1115.037</v>
       </c>
       <c r="G100">
         <v>49.4</v>
@@ -9493,37 +9493,37 @@
         <v>127.425</v>
       </c>
       <c r="M100">
-        <v>221.6378192</v>
+        <v>223.8994296</v>
       </c>
       <c r="N100">
-        <v>-94.2128192</v>
+        <v>-96.47442960000002</v>
       </c>
       <c r="O100">
-        <v>-9.42128192</v>
+        <v>-9.647442960000003</v>
       </c>
       <c r="P100">
-        <v>-84.79153728</v>
+        <v>-86.82698664000002</v>
       </c>
       <c r="Q100">
-        <v>-26.09153728</v>
+        <v>-28.12698664000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.975730676621293</v>
+        <v>3.905661353242584</v>
       </c>
       <c r="T100">
-        <v>38.68287426182754</v>
+        <v>77.36574852365507</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.05749244441221249</v>
+        <v>0.05691171265047296</v>
       </c>
       <c r="W100">
-        <v>0.1892555171620277</v>
+        <v>0.189372128099785</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5749244441221248</v>
+        <v>0.5691171265047296</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.226535020351213</v>
-      </c>
-      <c r="C101">
-        <v>-801.7504688417577</v>
-      </c>
-      <c r="D101">
-        <v>263.8865311582424</v>
-      </c>
-      <c r="E101">
-        <v>531.2370000000001</v>
-      </c>
-      <c r="F101">
-        <v>1115.037</v>
-      </c>
-      <c r="G101">
-        <v>49.4</v>
-      </c>
-      <c r="H101">
-        <v>542.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>186.125</v>
-      </c>
-      <c r="K101">
-        <v>58.7</v>
-      </c>
-      <c r="L101">
-        <v>127.425</v>
-      </c>
-      <c r="M101">
-        <v>223.8994296</v>
-      </c>
-      <c r="N101">
-        <v>-96.47442960000002</v>
-      </c>
-      <c r="O101">
-        <v>-9.647442960000003</v>
-      </c>
-      <c r="P101">
-        <v>-86.82698664000002</v>
-      </c>
-      <c r="Q101">
-        <v>-28.12698664000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.905661353242584</v>
-      </c>
-      <c r="T101">
-        <v>77.36574852365507</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.05691171265047296</v>
-      </c>
-      <c r="W101">
-        <v>0.189372128099785</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5691171265047296</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
